--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787609</v>
+        <v>118787669</v>
       </c>
       <c r="B8" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715936</v>
+        <v>716054</v>
       </c>
       <c r="R8" t="n">
-        <v>6351658</v>
+        <v>6351534</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787669</v>
+        <v>118787700</v>
       </c>
       <c r="B9" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716054</v>
+        <v>716089</v>
       </c>
       <c r="R9" t="n">
-        <v>6351534</v>
+        <v>6351760</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787700</v>
+        <v>118787653</v>
       </c>
       <c r="B10" t="n">
-        <v>106120</v>
+        <v>105495</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,20 +1590,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716089</v>
+        <v>716128</v>
       </c>
       <c r="R10" t="n">
-        <v>6351760</v>
+        <v>6351284</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787653</v>
+        <v>118787735</v>
       </c>
       <c r="B11" t="n">
-        <v>105495</v>
+        <v>106120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716128</v>
+        <v>716068</v>
       </c>
       <c r="R11" t="n">
-        <v>6351284</v>
+        <v>6351879</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787735</v>
+        <v>118787609</v>
       </c>
       <c r="B12" t="n">
         <v>106120</v>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716068</v>
+        <v>715936</v>
       </c>
       <c r="R12" t="n">
-        <v>6351879</v>
+        <v>6351658</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787669</v>
+        <v>118787609</v>
       </c>
       <c r="B8" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716054</v>
+        <v>715936</v>
       </c>
       <c r="R8" t="n">
-        <v>6351534</v>
+        <v>6351658</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787700</v>
+        <v>118787669</v>
       </c>
       <c r="B9" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716089</v>
+        <v>716054</v>
       </c>
       <c r="R9" t="n">
-        <v>6351760</v>
+        <v>6351534</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787653</v>
+        <v>118787700</v>
       </c>
       <c r="B10" t="n">
-        <v>105495</v>
+        <v>106120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,20 +1590,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716128</v>
+        <v>716089</v>
       </c>
       <c r="R10" t="n">
-        <v>6351284</v>
+        <v>6351760</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787735</v>
+        <v>118787653</v>
       </c>
       <c r="B11" t="n">
-        <v>106120</v>
+        <v>105495</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,20 +1697,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716068</v>
+        <v>716128</v>
       </c>
       <c r="R11" t="n">
-        <v>6351879</v>
+        <v>6351284</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787609</v>
+        <v>118787735</v>
       </c>
       <c r="B12" t="n">
         <v>106120</v>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715936</v>
+        <v>716068</v>
       </c>
       <c r="R12" t="n">
-        <v>6351658</v>
+        <v>6351879</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118787729</v>
+        <v>118787667</v>
       </c>
       <c r="B26" t="n">
-        <v>106776</v>
+        <v>106655</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3366,34 +3366,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716049</v>
+        <v>716086</v>
       </c>
       <c r="R26" t="n">
-        <v>6351866</v>
+        <v>6351456</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3457,10 +3466,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118787722</v>
+        <v>118787671</v>
       </c>
       <c r="B27" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3473,21 +3482,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3497,10 +3506,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716046</v>
+        <v>716074</v>
       </c>
       <c r="R27" t="n">
-        <v>6351830</v>
+        <v>6351539</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3564,7 +3573,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118787671</v>
+        <v>118787581</v>
       </c>
       <c r="B28" t="n">
         <v>106120</v>
@@ -3604,10 +3613,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716074</v>
+        <v>715987</v>
       </c>
       <c r="R28" t="n">
-        <v>6351539</v>
+        <v>6351753</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3671,10 +3680,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118787581</v>
+        <v>118787590</v>
       </c>
       <c r="B29" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3687,16 +3696,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3711,10 +3720,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715987</v>
+        <v>715935</v>
       </c>
       <c r="R29" t="n">
-        <v>6351753</v>
+        <v>6351703</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3778,10 +3787,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118787590</v>
+        <v>118794857</v>
       </c>
       <c r="B30" t="n">
-        <v>105736</v>
+        <v>57993</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3794,37 +3803,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221903</v>
+        <v>103055</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715935</v>
+        <v>715968</v>
       </c>
       <c r="R30" t="n">
-        <v>6351703</v>
+        <v>6351687</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3885,10 +3903,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118794857</v>
+        <v>118787729</v>
       </c>
       <c r="B31" t="n">
-        <v>57993</v>
+        <v>106776</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3901,46 +3919,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103055</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715968</v>
+        <v>716049</v>
       </c>
       <c r="R31" t="n">
-        <v>6351687</v>
+        <v>6351866</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4001,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118787667</v>
+        <v>118787722</v>
       </c>
       <c r="B32" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4017,43 +4026,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716086</v>
+        <v>716046</v>
       </c>
       <c r="R32" t="n">
-        <v>6351456</v>
+        <v>6351830</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118787630</v>
+        <v>118787650</v>
       </c>
       <c r="B3" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -844,17 +844,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716025</v>
+        <v>716014</v>
       </c>
       <c r="R3" t="n">
-        <v>6351589</v>
+        <v>6351357</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -918,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118787593</v>
+        <v>118787645</v>
       </c>
       <c r="B4" t="n">
-        <v>106776</v>
+        <v>105495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715906</v>
+        <v>715913</v>
       </c>
       <c r="R4" t="n">
-        <v>6351711</v>
+        <v>6351320</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,7 +1016,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1025,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118787577</v>
+        <v>118787608</v>
       </c>
       <c r="B5" t="n">
-        <v>106655</v>
+        <v>105736</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,16 +1050,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,26 +1067,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716038</v>
+        <v>715936</v>
       </c>
       <c r="R5" t="n">
-        <v>6351750</v>
+        <v>6351658</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118787633</v>
+        <v>118787579</v>
       </c>
       <c r="B6" t="n">
-        <v>106120</v>
+        <v>98469</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,34 +1157,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221849</v>
+        <v>222295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716028</v>
+        <v>715987</v>
       </c>
       <c r="R6" t="n">
-        <v>6351513</v>
+        <v>6351753</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,6 +1226,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1262,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118787652</v>
+        <v>118787687</v>
       </c>
       <c r="B7" t="n">
         <v>106655</v>
@@ -1283,7 +1297,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1297,10 +1311,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716032</v>
+        <v>716097</v>
       </c>
       <c r="R7" t="n">
-        <v>6351369</v>
+        <v>6351644</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1335,6 +1349,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,7 +1365,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1364,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787609</v>
+        <v>118787596</v>
       </c>
       <c r="B8" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,16 +1399,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1404,10 +1423,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715936</v>
+        <v>715882</v>
       </c>
       <c r="R8" t="n">
-        <v>6351658</v>
+        <v>6351669</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,7 +1472,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1471,10 +1490,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787669</v>
+        <v>118787600</v>
       </c>
       <c r="B9" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,21 +1506,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1530,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716054</v>
+        <v>715881</v>
       </c>
       <c r="R9" t="n">
-        <v>6351534</v>
+        <v>6351621</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1578,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787700</v>
+        <v>118787613</v>
       </c>
       <c r="B10" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,16 +1613,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1618,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716089</v>
+        <v>715954</v>
       </c>
       <c r="R10" t="n">
-        <v>6351760</v>
+        <v>6351671</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1686,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787653</v>
+        <v>118787734</v>
       </c>
       <c r="B11" t="n">
-        <v>105495</v>
+        <v>106776</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,25 +1716,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1725,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716128</v>
+        <v>716068</v>
       </c>
       <c r="R11" t="n">
-        <v>6351284</v>
+        <v>6351879</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1793,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1792,7 +1811,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787735</v>
+        <v>118787723</v>
       </c>
       <c r="B12" t="n">
         <v>106120</v>
@@ -1832,10 +1851,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716068</v>
+        <v>716046</v>
       </c>
       <c r="R12" t="n">
-        <v>6351879</v>
+        <v>6351830</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118787588</v>
+        <v>118787754</v>
       </c>
       <c r="B13" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,16 +1934,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1939,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715957</v>
+        <v>716069</v>
       </c>
       <c r="R13" t="n">
-        <v>6351748</v>
+        <v>6351918</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2006,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118787732</v>
+        <v>118787590</v>
       </c>
       <c r="B14" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,16 +2041,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2046,10 +2065,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716063</v>
+        <v>715935</v>
       </c>
       <c r="R14" t="n">
-        <v>6351869</v>
+        <v>6351703</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2113,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118787645</v>
+        <v>118787676</v>
       </c>
       <c r="B15" t="n">
-        <v>105495</v>
+        <v>106655</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,20 +2144,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>1865</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2146,17 +2165,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715913</v>
+        <v>716116</v>
       </c>
       <c r="R15" t="n">
-        <v>6351320</v>
+        <v>6351568</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2202,7 +2230,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2220,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118787579</v>
+        <v>118787677</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>106776</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,43 +2264,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222295</v>
+        <v>220079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715987</v>
+        <v>716116</v>
       </c>
       <c r="R16" t="n">
-        <v>6351753</v>
+        <v>6351568</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2305,11 +2324,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2341,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118787650</v>
+        <v>118787704</v>
       </c>
       <c r="B17" t="n">
-        <v>106655</v>
+        <v>103360</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2357,43 +2371,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1865</v>
+        <v>220164</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716014</v>
+        <v>716089</v>
       </c>
       <c r="R17" t="n">
-        <v>6351357</v>
+        <v>6351790</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2457,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118787723</v>
+        <v>118787686</v>
       </c>
       <c r="B18" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2473,21 +2478,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716046</v>
+        <v>716097</v>
       </c>
       <c r="R18" t="n">
-        <v>6351830</v>
+        <v>6351644</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2564,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118787608</v>
+        <v>118787752</v>
       </c>
       <c r="B19" t="n">
-        <v>105736</v>
+        <v>103360</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2580,21 +2585,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2604,10 +2609,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715936</v>
+        <v>716069</v>
       </c>
       <c r="R19" t="n">
-        <v>6351658</v>
+        <v>6351918</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2653,7 +2658,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2671,7 +2676,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118787705</v>
+        <v>118787666</v>
       </c>
       <c r="B20" t="n">
         <v>106655</v>
@@ -2706,7 +2711,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2720,10 +2725,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716089</v>
+        <v>716106</v>
       </c>
       <c r="R20" t="n">
-        <v>6351790</v>
+        <v>6351403</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2758,6 +2763,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2769,7 +2779,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2787,10 +2797,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118787676</v>
+        <v>118787735</v>
       </c>
       <c r="B21" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2803,16 +2813,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2820,26 +2830,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716116</v>
+        <v>716068</v>
       </c>
       <c r="R21" t="n">
-        <v>6351568</v>
+        <v>6351879</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2903,10 +2904,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118787599</v>
+        <v>118787617</v>
       </c>
       <c r="B22" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2919,16 +2920,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2943,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715881</v>
+        <v>715968</v>
       </c>
       <c r="R22" t="n">
-        <v>6351621</v>
+        <v>6351681</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2992,7 +2993,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3010,10 +3011,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118787755</v>
+        <v>118787616</v>
       </c>
       <c r="B23" t="n">
-        <v>105495</v>
+        <v>106120</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3022,20 +3023,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3050,10 +3051,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716067</v>
+        <v>715954</v>
       </c>
       <c r="R23" t="n">
-        <v>6351944</v>
+        <v>6351671</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3088,11 +3089,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3104,7 +3100,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3229,10 +3225,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118787629</v>
+        <v>118787609</v>
       </c>
       <c r="B25" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3245,16 +3241,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3262,26 +3258,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716025</v>
+        <v>715936</v>
       </c>
       <c r="R25" t="n">
-        <v>6351589</v>
+        <v>6351658</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3316,11 +3303,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3332,7 +3314,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3350,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118787667</v>
+        <v>118787711</v>
       </c>
       <c r="B26" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3366,16 +3348,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3383,26 +3365,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716086</v>
+        <v>716078</v>
       </c>
       <c r="R26" t="n">
-        <v>6351456</v>
+        <v>6351809</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3466,10 +3439,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118787671</v>
+        <v>118787651</v>
       </c>
       <c r="B27" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3482,16 +3455,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3499,17 +3472,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716074</v>
+        <v>716014</v>
       </c>
       <c r="R27" t="n">
-        <v>6351539</v>
+        <v>6351361</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3573,10 +3555,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118787581</v>
+        <v>118787641</v>
       </c>
       <c r="B28" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3589,34 +3571,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715987</v>
+        <v>715886</v>
       </c>
       <c r="R28" t="n">
-        <v>6351753</v>
+        <v>6351326</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3662,7 +3653,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3680,10 +3671,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118787590</v>
+        <v>118787592</v>
       </c>
       <c r="B29" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3696,16 +3687,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3720,10 +3711,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715935</v>
+        <v>715921</v>
       </c>
       <c r="R29" t="n">
-        <v>6351703</v>
+        <v>6351722</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3787,10 +3778,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118794857</v>
+        <v>118787587</v>
       </c>
       <c r="B30" t="n">
-        <v>57993</v>
+        <v>105736</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3803,46 +3794,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103055</v>
+        <v>221903</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715968</v>
+        <v>715957</v>
       </c>
       <c r="R30" t="n">
-        <v>6351687</v>
+        <v>6351748</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3903,10 +3885,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118787729</v>
+        <v>118787603</v>
       </c>
       <c r="B31" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3919,21 +3901,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3943,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716049</v>
+        <v>715907</v>
       </c>
       <c r="R31" t="n">
-        <v>6351866</v>
+        <v>6351637</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3992,7 +3974,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4010,10 +3992,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118787722</v>
+        <v>118787777</v>
       </c>
       <c r="B32" t="n">
-        <v>106776</v>
+        <v>42699</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4026,34 +4008,53 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220079</v>
+        <v>101070</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716046</v>
+        <v>716078</v>
       </c>
       <c r="R32" t="n">
-        <v>6351830</v>
+        <v>6351809</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4099,7 +4100,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4117,10 +4118,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118787678</v>
+        <v>118787684</v>
       </c>
       <c r="B33" t="n">
-        <v>106120</v>
+        <v>103360</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4133,21 +4134,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4157,13 +4158,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>716116</v>
+        <v>716101</v>
       </c>
       <c r="R33" t="n">
-        <v>6351568</v>
+        <v>6351620</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4224,10 +4225,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118787730</v>
+        <v>118787669</v>
       </c>
       <c r="B34" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4240,21 +4241,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4264,10 +4265,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>716049</v>
+        <v>716054</v>
       </c>
       <c r="R34" t="n">
-        <v>6351866</v>
+        <v>6351534</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4331,7 +4332,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118787673</v>
+        <v>118787693</v>
       </c>
       <c r="B35" t="n">
         <v>106776</v>
@@ -4371,10 +4372,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>716097</v>
+        <v>716098</v>
       </c>
       <c r="R35" t="n">
-        <v>6351540</v>
+        <v>6351710</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4438,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118787651</v>
+        <v>118787604</v>
       </c>
       <c r="B36" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4454,16 +4455,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4471,26 +4472,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>716014</v>
+        <v>715937</v>
       </c>
       <c r="R36" t="n">
-        <v>6351361</v>
+        <v>6351646</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4536,7 +4528,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4554,10 +4546,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118787685</v>
+        <v>118787633</v>
       </c>
       <c r="B37" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4570,16 +4562,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4587,26 +4579,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>716101</v>
+        <v>716028</v>
       </c>
       <c r="R37" t="n">
-        <v>6351620</v>
+        <v>6351513</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4670,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118787703</v>
+        <v>118787649</v>
       </c>
       <c r="B38" t="n">
-        <v>99504</v>
+        <v>106120</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4686,43 +4669,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716089</v>
+        <v>715990</v>
       </c>
       <c r="R38" t="n">
-        <v>6351790</v>
+        <v>6351309</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4768,7 +4742,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4786,7 +4760,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118787682</v>
+        <v>118787576</v>
       </c>
       <c r="B39" t="n">
         <v>106120</v>
@@ -4826,10 +4800,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716105</v>
+        <v>716038</v>
       </c>
       <c r="R39" t="n">
-        <v>6351578</v>
+        <v>6351750</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4893,10 +4867,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118787584</v>
+        <v>118787725</v>
       </c>
       <c r="B40" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4909,16 +4883,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4933,10 +4907,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>715975</v>
+        <v>716048</v>
       </c>
       <c r="R40" t="n">
-        <v>6351761</v>
+        <v>6351840</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5000,10 +4974,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118787649</v>
+        <v>118787721</v>
       </c>
       <c r="B41" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5016,16 +4990,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5033,17 +5007,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>715990</v>
+        <v>716046</v>
       </c>
       <c r="R41" t="n">
-        <v>6351309</v>
+        <v>6351830</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5107,10 +5090,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118787592</v>
+        <v>118787629</v>
       </c>
       <c r="B42" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5123,16 +5106,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5140,17 +5123,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715921</v>
+        <v>716025</v>
       </c>
       <c r="R42" t="n">
-        <v>6351722</v>
+        <v>6351589</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5183,6 +5175,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5214,10 +5211,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118787713</v>
+        <v>118787688</v>
       </c>
       <c r="B43" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5230,16 +5227,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5247,17 +5244,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716068</v>
+        <v>716083</v>
       </c>
       <c r="R43" t="n">
-        <v>6351807</v>
+        <v>6351660</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5290,6 +5296,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5321,7 +5332,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118787693</v>
+        <v>118787680</v>
       </c>
       <c r="B44" t="n">
         <v>106776</v>
@@ -5361,10 +5372,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716098</v>
+        <v>716111</v>
       </c>
       <c r="R44" t="n">
-        <v>6351710</v>
+        <v>6351576</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5397,6 +5408,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5428,10 +5444,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118787754</v>
+        <v>118787653</v>
       </c>
       <c r="B45" t="n">
-        <v>105736</v>
+        <v>105495</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5440,20 +5456,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221903</v>
+        <v>220785</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5468,13 +5484,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716069</v>
+        <v>716128</v>
       </c>
       <c r="R45" t="n">
-        <v>6351918</v>
+        <v>6351284</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5517,7 +5533,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5535,10 +5551,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118787751</v>
+        <v>118787755</v>
       </c>
       <c r="B46" t="n">
-        <v>106776</v>
+        <v>105495</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5547,25 +5563,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5575,13 +5591,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716069</v>
+        <v>716067</v>
       </c>
       <c r="R46" t="n">
-        <v>6351918</v>
+        <v>6351944</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5611,6 +5627,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5642,7 +5663,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118787731</v>
+        <v>118787637</v>
       </c>
       <c r="B47" t="n">
         <v>106776</v>
@@ -5682,13 +5703,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716063</v>
+        <v>715847</v>
       </c>
       <c r="R47" t="n">
-        <v>6351869</v>
+        <v>6351378</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5731,7 +5752,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5749,10 +5770,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118787627</v>
+        <v>118787668</v>
       </c>
       <c r="B48" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5765,21 +5786,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5789,10 +5810,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715996</v>
+        <v>716076</v>
       </c>
       <c r="R48" t="n">
-        <v>6351660</v>
+        <v>6351474</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5825,6 +5846,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5856,10 +5882,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118787772</v>
+        <v>118787628</v>
       </c>
       <c r="B49" t="n">
-        <v>42699</v>
+        <v>106120</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5872,53 +5898,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101070</v>
+        <v>221849</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715921</v>
+        <v>715996</v>
       </c>
       <c r="R49" t="n">
-        <v>6351722</v>
+        <v>6351660</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5961,6 +5968,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6084,7 +6096,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118787642</v>
+        <v>118787586</v>
       </c>
       <c r="B51" t="n">
         <v>106776</v>
@@ -6124,13 +6136,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715897</v>
+        <v>715957</v>
       </c>
       <c r="R51" t="n">
-        <v>6351335</v>
+        <v>6351748</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6173,7 +6185,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6191,10 +6203,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118787580</v>
+        <v>118787627</v>
       </c>
       <c r="B52" t="n">
-        <v>103360</v>
+        <v>106776</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6207,21 +6219,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6231,10 +6243,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715987</v>
+        <v>715996</v>
       </c>
       <c r="R52" t="n">
-        <v>6351753</v>
+        <v>6351660</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6298,10 +6310,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118787756</v>
+        <v>118787703</v>
       </c>
       <c r="B53" t="n">
-        <v>105736</v>
+        <v>99504</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6314,37 +6326,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221903</v>
+        <v>222617</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716067</v>
+        <v>716089</v>
       </c>
       <c r="R53" t="n">
-        <v>6351944</v>
+        <v>6351790</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6376,11 +6397,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6392,7 +6408,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6410,7 +6426,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118787668</v>
+        <v>118787695</v>
       </c>
       <c r="B54" t="n">
         <v>106120</v>
@@ -6450,13 +6466,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716076</v>
+        <v>716099</v>
       </c>
       <c r="R54" t="n">
-        <v>6351474</v>
+        <v>6351734</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6486,11 +6502,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6522,7 +6533,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118787670</v>
+        <v>118787583</v>
       </c>
       <c r="B55" t="n">
         <v>106776</v>
@@ -6562,10 +6573,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716074</v>
+        <v>715975</v>
       </c>
       <c r="R55" t="n">
-        <v>6351539</v>
+        <v>6351761</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6629,7 +6640,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118787600</v>
+        <v>118787700</v>
       </c>
       <c r="B56" t="n">
         <v>106120</v>
@@ -6669,10 +6680,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715881</v>
+        <v>716089</v>
       </c>
       <c r="R56" t="n">
-        <v>6351621</v>
+        <v>6351760</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6736,10 +6747,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118787698</v>
+        <v>118787678</v>
       </c>
       <c r="B57" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6752,16 +6763,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6769,26 +6780,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716099</v>
+        <v>716116</v>
       </c>
       <c r="R57" t="n">
-        <v>6351734</v>
+        <v>6351568</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6852,10 +6854,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118787677</v>
+        <v>118787585</v>
       </c>
       <c r="B58" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6868,21 +6870,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6892,10 +6894,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716116</v>
+        <v>715975</v>
       </c>
       <c r="R58" t="n">
-        <v>6351568</v>
+        <v>6351761</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6959,10 +6961,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118787639</v>
+        <v>118787756</v>
       </c>
       <c r="B59" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6975,16 +6977,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6999,10 +7001,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>715847</v>
+        <v>716067</v>
       </c>
       <c r="R59" t="n">
-        <v>6351378</v>
+        <v>6351944</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7037,6 +7039,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7048,7 +7055,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7066,10 +7073,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118787704</v>
+        <v>118787595</v>
       </c>
       <c r="B60" t="n">
-        <v>103360</v>
+        <v>106120</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7082,21 +7089,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7106,10 +7113,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716089</v>
+        <v>715904</v>
       </c>
       <c r="R60" t="n">
-        <v>6351790</v>
+        <v>6351691</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7155,7 +7162,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7173,10 +7180,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118787613</v>
+        <v>118787591</v>
       </c>
       <c r="B61" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7189,16 +7196,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7213,10 +7220,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715954</v>
+        <v>715935</v>
       </c>
       <c r="R61" t="n">
-        <v>6351671</v>
+        <v>6351703</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7262,7 +7269,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7280,7 +7287,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118787680</v>
+        <v>118787593</v>
       </c>
       <c r="B62" t="n">
         <v>106776</v>
@@ -7320,10 +7327,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>716111</v>
+        <v>715906</v>
       </c>
       <c r="R62" t="n">
-        <v>6351576</v>
+        <v>6351711</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7356,11 +7363,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7392,7 +7394,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118787684</v>
+        <v>118787580</v>
       </c>
       <c r="B63" t="n">
         <v>103360</v>
@@ -7432,13 +7434,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716101</v>
+        <v>715987</v>
       </c>
       <c r="R63" t="n">
-        <v>6351620</v>
+        <v>6351753</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7499,10 +7501,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118787720</v>
+        <v>118787718</v>
       </c>
       <c r="B64" t="n">
-        <v>98469</v>
+        <v>105736</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7515,33 +7517,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222295</v>
+        <v>221903</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
@@ -7584,11 +7577,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7620,10 +7608,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118787687</v>
+        <v>118787682</v>
       </c>
       <c r="B65" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7636,16 +7624,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7653,26 +7641,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716097</v>
+        <v>716105</v>
       </c>
       <c r="R65" t="n">
-        <v>6351644</v>
+        <v>6351578</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7707,11 +7686,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7723,7 +7697,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7741,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787724</v>
+        <v>118787584</v>
       </c>
       <c r="B66" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7757,21 +7731,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7781,10 +7755,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716048</v>
+        <v>715975</v>
       </c>
       <c r="R66" t="n">
-        <v>6351840</v>
+        <v>6351761</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7848,7 +7822,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787603</v>
+        <v>118787671</v>
       </c>
       <c r="B67" t="n">
         <v>106120</v>
@@ -7888,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715907</v>
+        <v>716074</v>
       </c>
       <c r="R67" t="n">
-        <v>6351637</v>
+        <v>6351539</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7937,7 +7911,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7955,7 +7929,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787637</v>
+        <v>118787751</v>
       </c>
       <c r="B68" t="n">
         <v>106776</v>
@@ -7995,13 +7969,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715847</v>
+        <v>716069</v>
       </c>
       <c r="R68" t="n">
-        <v>6351378</v>
+        <v>6351918</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8044,7 +8018,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8062,10 +8036,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787695</v>
+        <v>118787722</v>
       </c>
       <c r="B69" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8078,21 +8052,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8102,13 +8076,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716099</v>
+        <v>716046</v>
       </c>
       <c r="R69" t="n">
-        <v>6351734</v>
+        <v>6351830</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8169,10 +8143,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787591</v>
+        <v>118787698</v>
       </c>
       <c r="B70" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8185,16 +8159,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8202,17 +8176,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715935</v>
+        <v>716099</v>
       </c>
       <c r="R70" t="n">
-        <v>6351703</v>
+        <v>6351734</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8276,10 +8259,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787777</v>
+        <v>118787622</v>
       </c>
       <c r="B71" t="n">
-        <v>42699</v>
+        <v>105736</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8292,53 +8275,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>101070</v>
+        <v>221903</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>716078</v>
+        <v>715968</v>
       </c>
       <c r="R71" t="n">
-        <v>6351809</v>
+        <v>6351681</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8384,7 +8348,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8402,10 +8366,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118787688</v>
+        <v>118787713</v>
       </c>
       <c r="B72" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8418,16 +8382,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8435,26 +8399,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716083</v>
+        <v>716068</v>
       </c>
       <c r="R72" t="n">
-        <v>6351660</v>
+        <v>6351807</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8487,11 +8442,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8523,10 +8473,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118787586</v>
+        <v>118787727</v>
       </c>
       <c r="B73" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8539,21 +8489,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8563,13 +8513,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715957</v>
+        <v>716051</v>
       </c>
       <c r="R73" t="n">
-        <v>6351748</v>
+        <v>6351855</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8630,10 +8580,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118787604</v>
+        <v>118787673</v>
       </c>
       <c r="B74" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8646,21 +8596,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8670,10 +8620,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>715937</v>
+        <v>716097</v>
       </c>
       <c r="R74" t="n">
-        <v>6351646</v>
+        <v>6351540</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8719,7 +8669,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8737,10 +8687,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118787643</v>
+        <v>118787685</v>
       </c>
       <c r="B75" t="n">
-        <v>100107</v>
+        <v>106655</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8749,38 +8699,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>1865</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715897</v>
+        <v>716101</v>
       </c>
       <c r="R75" t="n">
-        <v>6351335</v>
+        <v>6351620</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8826,7 +8785,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8844,10 +8803,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118787617</v>
+        <v>118787652</v>
       </c>
       <c r="B76" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8860,16 +8819,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8877,17 +8836,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715968</v>
+        <v>716032</v>
       </c>
       <c r="R76" t="n">
-        <v>6351681</v>
+        <v>6351369</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8933,7 +8901,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8951,10 +8919,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118787622</v>
+        <v>118787772</v>
       </c>
       <c r="B77" t="n">
-        <v>105736</v>
+        <v>42699</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8967,34 +8935,53 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221903</v>
+        <v>101070</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715968</v>
+        <v>715921</v>
       </c>
       <c r="R77" t="n">
-        <v>6351681</v>
+        <v>6351722</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9037,11 +9024,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9058,10 +9040,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118787721</v>
+        <v>118787632</v>
       </c>
       <c r="B78" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9074,43 +9056,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716046</v>
+        <v>716028</v>
       </c>
       <c r="R78" t="n">
-        <v>6351830</v>
+        <v>6351513</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9174,10 +9147,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118787752</v>
+        <v>118787670</v>
       </c>
       <c r="B79" t="n">
-        <v>103360</v>
+        <v>106776</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9190,21 +9163,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9214,10 +9187,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>716069</v>
+        <v>716074</v>
       </c>
       <c r="R79" t="n">
-        <v>6351918</v>
+        <v>6351539</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9281,10 +9254,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118787595</v>
+        <v>118787643</v>
       </c>
       <c r="B80" t="n">
-        <v>106120</v>
+        <v>100107</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9293,25 +9266,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221849</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9321,10 +9294,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715904</v>
+        <v>715897</v>
       </c>
       <c r="R80" t="n">
-        <v>6351691</v>
+        <v>6351335</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9370,7 +9343,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9388,10 +9361,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118787596</v>
+        <v>118787639</v>
       </c>
       <c r="B81" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9404,16 +9377,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9428,13 +9401,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715882</v>
+        <v>715847</v>
       </c>
       <c r="R81" t="n">
-        <v>6351669</v>
+        <v>6351378</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9477,7 +9450,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9495,7 +9468,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118787727</v>
+        <v>118787730</v>
       </c>
       <c r="B82" t="n">
         <v>106120</v>
@@ -9535,10 +9508,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716051</v>
+        <v>716049</v>
       </c>
       <c r="R82" t="n">
-        <v>6351855</v>
+        <v>6351866</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9602,7 +9575,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118787711</v>
+        <v>118787594</v>
       </c>
       <c r="B83" t="n">
         <v>106120</v>
@@ -9642,10 +9615,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>716078</v>
+        <v>715906</v>
       </c>
       <c r="R83" t="n">
-        <v>6351809</v>
+        <v>6351711</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9709,10 +9682,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118787583</v>
+        <v>118787599</v>
       </c>
       <c r="B84" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9725,21 +9698,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9749,10 +9722,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715975</v>
+        <v>715881</v>
       </c>
       <c r="R84" t="n">
-        <v>6351761</v>
+        <v>6351621</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9816,10 +9789,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118787734</v>
+        <v>118794857</v>
       </c>
       <c r="B85" t="n">
-        <v>106776</v>
+        <v>57993</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9832,37 +9805,46 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>716068</v>
+        <v>715968</v>
       </c>
       <c r="R85" t="n">
-        <v>6351879</v>
+        <v>6351687</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9923,10 +9905,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118787628</v>
+        <v>118787726</v>
       </c>
       <c r="B86" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9939,21 +9921,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9963,10 +9945,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715996</v>
+        <v>716051</v>
       </c>
       <c r="R86" t="n">
-        <v>6351660</v>
+        <v>6351855</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10030,10 +10012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118787585</v>
+        <v>118787642</v>
       </c>
       <c r="B87" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10046,21 +10028,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10070,10 +10052,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715975</v>
+        <v>715897</v>
       </c>
       <c r="R87" t="n">
-        <v>6351761</v>
+        <v>6351335</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10119,7 +10101,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10137,10 +10119,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118787576</v>
+        <v>118787729</v>
       </c>
       <c r="B88" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10153,21 +10135,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10177,10 +10159,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>716038</v>
+        <v>716049</v>
       </c>
       <c r="R88" t="n">
-        <v>6351750</v>
+        <v>6351866</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10244,10 +10226,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118787587</v>
+        <v>118787581</v>
       </c>
       <c r="B89" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10260,16 +10242,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10284,10 +10266,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715957</v>
+        <v>715987</v>
       </c>
       <c r="R89" t="n">
-        <v>6351748</v>
+        <v>6351753</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10351,7 +10333,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118787594</v>
+        <v>118787630</v>
       </c>
       <c r="B90" t="n">
         <v>106120</v>
@@ -10391,10 +10373,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715906</v>
+        <v>716025</v>
       </c>
       <c r="R90" t="n">
-        <v>6351711</v>
+        <v>6351589</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10458,10 +10440,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118787686</v>
+        <v>118787720</v>
       </c>
       <c r="B91" t="n">
-        <v>106776</v>
+        <v>98469</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10474,34 +10456,43 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220079</v>
+        <v>222295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>716097</v>
+        <v>716046</v>
       </c>
       <c r="R91" t="n">
-        <v>6351644</v>
+        <v>6351830</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10534,6 +10525,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10565,7 +10561,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118787616</v>
+        <v>118787588</v>
       </c>
       <c r="B92" t="n">
         <v>106120</v>
@@ -10605,13 +10601,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715954</v>
+        <v>715957</v>
       </c>
       <c r="R92" t="n">
-        <v>6351671</v>
+        <v>6351748</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10654,7 +10650,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10672,10 +10668,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118787725</v>
+        <v>118787577</v>
       </c>
       <c r="B93" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10688,16 +10684,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10705,17 +10701,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>716048</v>
+        <v>716038</v>
       </c>
       <c r="R93" t="n">
-        <v>6351840</v>
+        <v>6351750</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10779,10 +10784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118787718</v>
+        <v>118787705</v>
       </c>
       <c r="B94" t="n">
-        <v>105736</v>
+        <v>106655</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10795,16 +10800,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10812,17 +10817,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>716046</v>
+        <v>716089</v>
       </c>
       <c r="R94" t="n">
-        <v>6351830</v>
+        <v>6351790</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10868,7 +10882,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10886,10 +10900,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118787632</v>
+        <v>118787667</v>
       </c>
       <c r="B95" t="n">
-        <v>106776</v>
+        <v>106655</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10902,34 +10916,43 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716028</v>
+        <v>716086</v>
       </c>
       <c r="R95" t="n">
-        <v>6351513</v>
+        <v>6351456</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10993,10 +11016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118787666</v>
+        <v>118787724</v>
       </c>
       <c r="B96" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11009,43 +11032,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716106</v>
+        <v>716048</v>
       </c>
       <c r="R96" t="n">
-        <v>6351403</v>
+        <v>6351840</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11078,11 +11092,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11114,10 +11123,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118787712</v>
+        <v>118787731</v>
       </c>
       <c r="B97" t="n">
-        <v>105736</v>
+        <v>106776</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11130,21 +11139,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11154,10 +11163,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716068</v>
+        <v>716063</v>
       </c>
       <c r="R97" t="n">
-        <v>6351807</v>
+        <v>6351869</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11328,10 +11337,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787726</v>
+        <v>118787712</v>
       </c>
       <c r="B99" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11344,21 +11353,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11368,10 +11377,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716051</v>
+        <v>716068</v>
       </c>
       <c r="R99" t="n">
-        <v>6351855</v>
+        <v>6351807</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11435,7 +11444,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787753</v>
+        <v>118787732</v>
       </c>
       <c r="B100" t="n">
         <v>106120</v>
@@ -11475,10 +11484,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>716069</v>
+        <v>716063</v>
       </c>
       <c r="R100" t="n">
-        <v>6351918</v>
+        <v>6351869</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11542,10 +11551,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787641</v>
+        <v>118787753</v>
       </c>
       <c r="B101" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11558,43 +11567,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715886</v>
+        <v>716069</v>
       </c>
       <c r="R101" t="n">
-        <v>6351326</v>
+        <v>6351918</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -4653,10 +4653,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118787649</v>
+        <v>118787721</v>
       </c>
       <c r="B38" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4669,16 +4669,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4686,17 +4686,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715990</v>
+        <v>716046</v>
       </c>
       <c r="R38" t="n">
-        <v>6351309</v>
+        <v>6351830</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4760,7 +4769,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118787576</v>
+        <v>118787649</v>
       </c>
       <c r="B39" t="n">
         <v>106120</v>
@@ -4800,10 +4809,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716038</v>
+        <v>715990</v>
       </c>
       <c r="R39" t="n">
-        <v>6351750</v>
+        <v>6351309</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4867,7 +4876,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118787725</v>
+        <v>118787576</v>
       </c>
       <c r="B40" t="n">
         <v>106120</v>
@@ -4907,10 +4916,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716048</v>
+        <v>716038</v>
       </c>
       <c r="R40" t="n">
-        <v>6351840</v>
+        <v>6351750</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4974,10 +4983,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118787721</v>
+        <v>118787725</v>
       </c>
       <c r="B41" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4990,16 +4999,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5007,26 +5016,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716046</v>
+        <v>716048</v>
       </c>
       <c r="R41" t="n">
-        <v>6351830</v>
+        <v>6351840</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5090,10 +5090,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118787629</v>
+        <v>118787680</v>
       </c>
       <c r="B42" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5106,43 +5106,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716025</v>
+        <v>716111</v>
       </c>
       <c r="R42" t="n">
-        <v>6351589</v>
+        <v>6351576</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5179,7 +5170,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5211,10 +5202,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118787688</v>
+        <v>118787653</v>
       </c>
       <c r="B43" t="n">
-        <v>106655</v>
+        <v>105495</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5223,20 +5214,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1865</v>
+        <v>220785</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5244,29 +5235,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716083</v>
+        <v>716128</v>
       </c>
       <c r="R43" t="n">
-        <v>6351660</v>
+        <v>6351284</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5298,11 +5280,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5314,7 +5291,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5332,10 +5309,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118787680</v>
+        <v>118787755</v>
       </c>
       <c r="B44" t="n">
-        <v>106776</v>
+        <v>105495</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5344,25 +5321,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5372,13 +5349,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716111</v>
+        <v>716067</v>
       </c>
       <c r="R44" t="n">
-        <v>6351576</v>
+        <v>6351944</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5412,7 +5389,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5444,10 +5421,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118787653</v>
+        <v>118787637</v>
       </c>
       <c r="B45" t="n">
-        <v>105495</v>
+        <v>106776</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5456,25 +5433,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5484,10 +5461,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716128</v>
+        <v>715847</v>
       </c>
       <c r="R45" t="n">
-        <v>6351284</v>
+        <v>6351378</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5533,7 +5510,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5551,10 +5528,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118787755</v>
+        <v>118787629</v>
       </c>
       <c r="B46" t="n">
-        <v>105495</v>
+        <v>106655</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5563,20 +5540,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220785</v>
+        <v>1865</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5584,20 +5561,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716067</v>
+        <v>716025</v>
       </c>
       <c r="R46" t="n">
-        <v>6351944</v>
+        <v>6351589</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5631,7 +5617,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Svårframkomligt; slån, en.</t>
+          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5663,10 +5649,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118787637</v>
+        <v>118787688</v>
       </c>
       <c r="B47" t="n">
-        <v>106776</v>
+        <v>106655</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5679,37 +5665,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>715847</v>
+        <v>716083</v>
       </c>
       <c r="R47" t="n">
-        <v>6351378</v>
+        <v>6351660</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5741,6 +5736,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118787700</v>
+        <v>118787756</v>
       </c>
       <c r="B56" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6656,16 +6656,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6680,13 +6680,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716089</v>
+        <v>716067</v>
       </c>
       <c r="R56" t="n">
-        <v>6351760</v>
+        <v>6351944</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6716,6 +6716,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6747,7 +6752,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118787678</v>
+        <v>118787595</v>
       </c>
       <c r="B57" t="n">
         <v>106120</v>
@@ -6787,10 +6792,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716116</v>
+        <v>715904</v>
       </c>
       <c r="R57" t="n">
-        <v>6351568</v>
+        <v>6351691</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6854,7 +6859,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118787585</v>
+        <v>118787591</v>
       </c>
       <c r="B58" t="n">
         <v>106120</v>
@@ -6894,10 +6899,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715975</v>
+        <v>715935</v>
       </c>
       <c r="R58" t="n">
-        <v>6351761</v>
+        <v>6351703</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6961,10 +6966,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118787756</v>
+        <v>118787700</v>
       </c>
       <c r="B59" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6977,16 +6982,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -7001,13 +7006,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716067</v>
+        <v>716089</v>
       </c>
       <c r="R59" t="n">
-        <v>6351944</v>
+        <v>6351760</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7037,11 +7042,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7073,7 +7073,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118787595</v>
+        <v>118787678</v>
       </c>
       <c r="B60" t="n">
         <v>106120</v>
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715904</v>
+        <v>716116</v>
       </c>
       <c r="R60" t="n">
-        <v>6351691</v>
+        <v>6351568</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7180,7 +7180,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118787591</v>
+        <v>118787585</v>
       </c>
       <c r="B61" t="n">
         <v>106120</v>
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715935</v>
+        <v>715975</v>
       </c>
       <c r="R61" t="n">
-        <v>6351703</v>
+        <v>6351761</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7715,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787584</v>
+        <v>118787698</v>
       </c>
       <c r="B66" t="n">
-        <v>105736</v>
+        <v>106655</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7731,16 +7731,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7748,17 +7748,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>715975</v>
+        <v>716099</v>
       </c>
       <c r="R66" t="n">
-        <v>6351761</v>
+        <v>6351734</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7822,10 +7831,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787671</v>
+        <v>118787751</v>
       </c>
       <c r="B67" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7838,21 +7847,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7862,10 +7871,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716074</v>
+        <v>716069</v>
       </c>
       <c r="R67" t="n">
-        <v>6351539</v>
+        <v>6351918</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7929,7 +7938,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787751</v>
+        <v>118787722</v>
       </c>
       <c r="B68" t="n">
         <v>106776</v>
@@ -7969,10 +7978,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>716069</v>
+        <v>716046</v>
       </c>
       <c r="R68" t="n">
-        <v>6351918</v>
+        <v>6351830</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8036,10 +8045,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787722</v>
+        <v>118787622</v>
       </c>
       <c r="B69" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8052,21 +8061,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8076,10 +8085,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716046</v>
+        <v>715968</v>
       </c>
       <c r="R69" t="n">
-        <v>6351830</v>
+        <v>6351681</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8125,7 +8134,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8143,10 +8152,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787698</v>
+        <v>118787584</v>
       </c>
       <c r="B70" t="n">
-        <v>106655</v>
+        <v>105736</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8159,16 +8168,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8176,26 +8185,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716099</v>
+        <v>715975</v>
       </c>
       <c r="R70" t="n">
-        <v>6351734</v>
+        <v>6351761</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8259,10 +8259,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787622</v>
+        <v>118787671</v>
       </c>
       <c r="B71" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,16 +8275,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715968</v>
+        <v>716074</v>
       </c>
       <c r="R71" t="n">
-        <v>6351681</v>
+        <v>6351539</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -9361,10 +9361,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118787639</v>
+        <v>118794857</v>
       </c>
       <c r="B81" t="n">
-        <v>106120</v>
+        <v>57993</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9377,37 +9377,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221849</v>
+        <v>103055</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715847</v>
+        <v>715968</v>
       </c>
       <c r="R81" t="n">
-        <v>6351378</v>
+        <v>6351687</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9450,7 +9459,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9468,10 +9477,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118787730</v>
+        <v>118787726</v>
       </c>
       <c r="B82" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9484,21 +9493,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9508,10 +9517,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716049</v>
+        <v>716051</v>
       </c>
       <c r="R82" t="n">
-        <v>6351866</v>
+        <v>6351855</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9575,7 +9584,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118787594</v>
+        <v>118787639</v>
       </c>
       <c r="B83" t="n">
         <v>106120</v>
@@ -9615,13 +9624,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715906</v>
+        <v>715847</v>
       </c>
       <c r="R83" t="n">
-        <v>6351711</v>
+        <v>6351378</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9664,7 +9673,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9682,10 +9691,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118787599</v>
+        <v>118787730</v>
       </c>
       <c r="B84" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9698,16 +9707,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9722,10 +9731,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715881</v>
+        <v>716049</v>
       </c>
       <c r="R84" t="n">
-        <v>6351621</v>
+        <v>6351866</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9789,10 +9798,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118794857</v>
+        <v>118787594</v>
       </c>
       <c r="B85" t="n">
-        <v>57993</v>
+        <v>106120</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9805,46 +9814,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715968</v>
+        <v>715906</v>
       </c>
       <c r="R85" t="n">
-        <v>6351687</v>
+        <v>6351711</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9905,10 +9905,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118787726</v>
+        <v>118787599</v>
       </c>
       <c r="B86" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9921,21 +9921,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>716051</v>
+        <v>715881</v>
       </c>
       <c r="R86" t="n">
-        <v>6351855</v>
+        <v>6351621</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10012,10 +10012,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118787642</v>
+        <v>118787577</v>
       </c>
       <c r="B87" t="n">
-        <v>106776</v>
+        <v>106655</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10028,34 +10028,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715897</v>
+        <v>716038</v>
       </c>
       <c r="R87" t="n">
-        <v>6351335</v>
+        <v>6351750</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10101,7 +10110,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10119,10 +10128,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118787729</v>
+        <v>118787705</v>
       </c>
       <c r="B88" t="n">
-        <v>106776</v>
+        <v>106655</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10135,34 +10144,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>716049</v>
+        <v>716089</v>
       </c>
       <c r="R88" t="n">
-        <v>6351866</v>
+        <v>6351790</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10208,7 +10226,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10226,10 +10244,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118787581</v>
+        <v>118787667</v>
       </c>
       <c r="B89" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10242,16 +10260,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10259,17 +10277,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715987</v>
+        <v>716086</v>
       </c>
       <c r="R89" t="n">
-        <v>6351753</v>
+        <v>6351456</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10333,10 +10360,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118787630</v>
+        <v>118787642</v>
       </c>
       <c r="B90" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10349,21 +10376,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10373,10 +10400,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>716025</v>
+        <v>715897</v>
       </c>
       <c r="R90" t="n">
-        <v>6351589</v>
+        <v>6351335</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10422,7 +10449,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10440,10 +10467,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118787720</v>
+        <v>118787729</v>
       </c>
       <c r="B91" t="n">
-        <v>98469</v>
+        <v>106776</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10456,43 +10483,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222295</v>
+        <v>220079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>716046</v>
+        <v>716049</v>
       </c>
       <c r="R91" t="n">
-        <v>6351830</v>
+        <v>6351866</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10525,11 +10543,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10561,7 +10574,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118787588</v>
+        <v>118787630</v>
       </c>
       <c r="B92" t="n">
         <v>106120</v>
@@ -10601,10 +10614,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715957</v>
+        <v>716025</v>
       </c>
       <c r="R92" t="n">
-        <v>6351748</v>
+        <v>6351589</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10668,10 +10681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118787577</v>
+        <v>118787720</v>
       </c>
       <c r="B93" t="n">
-        <v>106655</v>
+        <v>98469</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10684,26 +10697,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1865</v>
+        <v>222295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -10717,10 +10730,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>716038</v>
+        <v>716046</v>
       </c>
       <c r="R93" t="n">
-        <v>6351750</v>
+        <v>6351830</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10753,6 +10766,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10784,10 +10802,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118787705</v>
+        <v>118787588</v>
       </c>
       <c r="B94" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10800,16 +10818,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10817,26 +10835,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>716089</v>
+        <v>715957</v>
       </c>
       <c r="R94" t="n">
-        <v>6351790</v>
+        <v>6351748</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10882,7 +10891,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10900,10 +10909,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118787667</v>
+        <v>118787581</v>
       </c>
       <c r="B95" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10916,16 +10925,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10933,26 +10942,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716086</v>
+        <v>715987</v>
       </c>
       <c r="R95" t="n">
-        <v>6351456</v>
+        <v>6351753</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11230,10 +11230,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118787681</v>
+        <v>118787712</v>
       </c>
       <c r="B98" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11246,16 +11246,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716111</v>
+        <v>716068</v>
       </c>
       <c r="R98" t="n">
-        <v>6351576</v>
+        <v>6351807</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11337,10 +11337,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787712</v>
+        <v>118787732</v>
       </c>
       <c r="B99" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11353,16 +11353,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716068</v>
+        <v>716063</v>
       </c>
       <c r="R99" t="n">
-        <v>6351807</v>
+        <v>6351869</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787732</v>
+        <v>118787753</v>
       </c>
       <c r="B100" t="n">
         <v>106120</v>
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>716063</v>
+        <v>716069</v>
       </c>
       <c r="R100" t="n">
-        <v>6351869</v>
+        <v>6351918</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11551,7 +11551,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787753</v>
+        <v>118787681</v>
       </c>
       <c r="B101" t="n">
         <v>106120</v>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>716069</v>
+        <v>716111</v>
       </c>
       <c r="R101" t="n">
-        <v>6351918</v>
+        <v>6351576</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118787650</v>
+        <v>118787643</v>
       </c>
       <c r="B3" t="n">
-        <v>106655</v>
+        <v>100107</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,47 +823,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1865</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716014</v>
+        <v>715897</v>
       </c>
       <c r="R3" t="n">
-        <v>6351357</v>
+        <v>6351335</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -909,7 +900,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -927,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118787645</v>
+        <v>118794857</v>
       </c>
       <c r="B4" t="n">
-        <v>105495</v>
+        <v>57993</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,41 +930,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715913</v>
+        <v>715968</v>
       </c>
       <c r="R4" t="n">
-        <v>6351320</v>
+        <v>6351687</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118787608</v>
+        <v>118787651</v>
       </c>
       <c r="B5" t="n">
-        <v>105736</v>
+        <v>106655</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,17 +1067,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715936</v>
+        <v>716014</v>
       </c>
       <c r="R5" t="n">
-        <v>6351658</v>
+        <v>6351361</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,7 +1132,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1141,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118787579</v>
+        <v>118787684</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>103360</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,46 +1166,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>220164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>715987</v>
+        <v>716101</v>
       </c>
       <c r="R6" t="n">
-        <v>6351753</v>
+        <v>6351620</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,11 +1226,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118787687</v>
+        <v>118787632</v>
       </c>
       <c r="B7" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,43 +1273,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716097</v>
+        <v>716028</v>
       </c>
       <c r="R7" t="n">
-        <v>6351644</v>
+        <v>6351513</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1349,11 +1335,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1365,7 +1346,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1383,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787596</v>
+        <v>118787639</v>
       </c>
       <c r="B8" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,16 +1380,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1423,13 +1404,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715882</v>
+        <v>715847</v>
       </c>
       <c r="R8" t="n">
-        <v>6351669</v>
+        <v>6351378</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1472,7 +1453,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1490,7 +1471,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787600</v>
+        <v>118787727</v>
       </c>
       <c r="B9" t="n">
         <v>106120</v>
@@ -1530,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>715881</v>
+        <v>716051</v>
       </c>
       <c r="R9" t="n">
-        <v>6351621</v>
+        <v>6351855</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1597,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787613</v>
+        <v>118787608</v>
       </c>
       <c r="B10" t="n">
         <v>105736</v>
@@ -1637,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715954</v>
+        <v>715936</v>
       </c>
       <c r="R10" t="n">
-        <v>6351671</v>
+        <v>6351658</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787734</v>
+        <v>118787712</v>
       </c>
       <c r="B11" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,21 +1701,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,7 +1728,7 @@
         <v>716068</v>
       </c>
       <c r="R11" t="n">
-        <v>6351879</v>
+        <v>6351807</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1811,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787723</v>
+        <v>118787686</v>
       </c>
       <c r="B12" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,21 +1808,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1851,10 +1832,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716046</v>
+        <v>716097</v>
       </c>
       <c r="R12" t="n">
-        <v>6351830</v>
+        <v>6351644</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1918,10 +1899,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118787754</v>
+        <v>118787670</v>
       </c>
       <c r="B13" t="n">
-        <v>105736</v>
+        <v>106776</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1915,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1939,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716069</v>
+        <v>716074</v>
       </c>
       <c r="R13" t="n">
-        <v>6351918</v>
+        <v>6351539</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2025,10 +2006,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118787590</v>
+        <v>118787711</v>
       </c>
       <c r="B14" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2041,16 +2022,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2065,10 +2046,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715935</v>
+        <v>716078</v>
       </c>
       <c r="R14" t="n">
-        <v>6351703</v>
+        <v>6351809</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2132,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118787676</v>
+        <v>118787616</v>
       </c>
       <c r="B15" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,16 +2129,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2165,29 +2146,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716116</v>
+        <v>715954</v>
       </c>
       <c r="R15" t="n">
-        <v>6351568</v>
+        <v>6351671</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2230,7 +2202,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2248,10 +2220,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118787677</v>
+        <v>118787671</v>
       </c>
       <c r="B16" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716116</v>
+        <v>716074</v>
       </c>
       <c r="R16" t="n">
-        <v>6351568</v>
+        <v>6351539</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,10 +2327,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118787704</v>
+        <v>118787667</v>
       </c>
       <c r="B17" t="n">
-        <v>103360</v>
+        <v>106655</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,34 +2343,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220164</v>
+        <v>1865</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716089</v>
+        <v>716086</v>
       </c>
       <c r="R17" t="n">
-        <v>6351790</v>
+        <v>6351456</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,7 +2425,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2443,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118787686</v>
+        <v>118787685</v>
       </c>
       <c r="B18" t="n">
-        <v>106776</v>
+        <v>106655</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,34 +2459,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716097</v>
+        <v>716101</v>
       </c>
       <c r="R18" t="n">
-        <v>6351644</v>
+        <v>6351620</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118787752</v>
+        <v>118787772</v>
       </c>
       <c r="B19" t="n">
-        <v>103360</v>
+        <v>42699</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,34 +2575,53 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220164</v>
+        <v>101070</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716069</v>
+        <v>715921</v>
       </c>
       <c r="R19" t="n">
-        <v>6351918</v>
+        <v>6351722</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2655,11 +2664,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2676,10 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118787666</v>
+        <v>118787693</v>
       </c>
       <c r="B20" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,43 +2696,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716106</v>
+        <v>716098</v>
       </c>
       <c r="R20" t="n">
-        <v>6351403</v>
+        <v>6351710</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2761,11 +2756,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2797,10 +2787,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118787735</v>
+        <v>118787627</v>
       </c>
       <c r="B21" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2813,21 +2803,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2837,10 +2827,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716068</v>
+        <v>715996</v>
       </c>
       <c r="R21" t="n">
-        <v>6351879</v>
+        <v>6351660</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2904,7 +2894,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118787617</v>
+        <v>118787732</v>
       </c>
       <c r="B22" t="n">
         <v>106120</v>
@@ -2944,10 +2934,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>715968</v>
+        <v>716063</v>
       </c>
       <c r="R22" t="n">
-        <v>6351681</v>
+        <v>6351869</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2993,7 +2983,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3011,10 +3001,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118787616</v>
+        <v>118787650</v>
       </c>
       <c r="B23" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3027,16 +3017,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3044,20 +3034,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715954</v>
+        <v>716014</v>
       </c>
       <c r="R23" t="n">
-        <v>6351671</v>
+        <v>6351357</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3100,7 +3099,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3118,10 +3117,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118787733</v>
+        <v>118787688</v>
       </c>
       <c r="B24" t="n">
-        <v>105736</v>
+        <v>106655</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3134,16 +3133,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3151,17 +3150,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716068</v>
+        <v>716083</v>
       </c>
       <c r="R24" t="n">
-        <v>6351879</v>
+        <v>6351660</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3194,6 +3202,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3225,10 +3238,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118787609</v>
+        <v>118787680</v>
       </c>
       <c r="B25" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3241,21 +3254,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3265,10 +3278,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715936</v>
+        <v>716111</v>
       </c>
       <c r="R25" t="n">
-        <v>6351658</v>
+        <v>6351576</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3303,6 +3316,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3314,7 +3332,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3332,10 +3350,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118787711</v>
+        <v>118787653</v>
       </c>
       <c r="B26" t="n">
-        <v>106120</v>
+        <v>105495</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,20 +3362,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3372,13 +3390,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716078</v>
+        <v>716128</v>
       </c>
       <c r="R26" t="n">
-        <v>6351809</v>
+        <v>6351284</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3421,7 +3439,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3439,10 +3457,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118787651</v>
+        <v>118787645</v>
       </c>
       <c r="B27" t="n">
-        <v>106655</v>
+        <v>105495</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3451,20 +3469,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1865</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3472,26 +3490,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716014</v>
+        <v>715913</v>
       </c>
       <c r="R27" t="n">
-        <v>6351361</v>
+        <v>6351320</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3537,7 +3546,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3555,10 +3564,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118787641</v>
+        <v>118787733</v>
       </c>
       <c r="B28" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3571,43 +3580,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715886</v>
+        <v>716068</v>
       </c>
       <c r="R28" t="n">
-        <v>6351326</v>
+        <v>6351879</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118787592</v>
+        <v>118787609</v>
       </c>
       <c r="B29" t="n">
         <v>106120</v>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715921</v>
+        <v>715936</v>
       </c>
       <c r="R29" t="n">
-        <v>6351722</v>
+        <v>6351658</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3778,10 +3778,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118787587</v>
+        <v>118787722</v>
       </c>
       <c r="B30" t="n">
-        <v>105736</v>
+        <v>106776</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3794,21 +3794,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715957</v>
+        <v>716046</v>
       </c>
       <c r="R30" t="n">
-        <v>6351748</v>
+        <v>6351830</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118787603</v>
+        <v>118787694</v>
       </c>
       <c r="B31" t="n">
         <v>106120</v>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715907</v>
+        <v>716098</v>
       </c>
       <c r="R31" t="n">
-        <v>6351637</v>
+        <v>6351710</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3992,10 +3992,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118787777</v>
+        <v>118787591</v>
       </c>
       <c r="B32" t="n">
-        <v>42699</v>
+        <v>106120</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4008,53 +4008,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101070</v>
+        <v>221849</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716078</v>
+        <v>715935</v>
       </c>
       <c r="R32" t="n">
-        <v>6351809</v>
+        <v>6351703</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4100,7 +4081,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4118,10 +4099,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118787684</v>
+        <v>118787676</v>
       </c>
       <c r="B33" t="n">
-        <v>103360</v>
+        <v>106655</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4134,37 +4115,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220164</v>
+        <v>1865</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>716101</v>
+        <v>716116</v>
       </c>
       <c r="R33" t="n">
-        <v>6351620</v>
+        <v>6351568</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4225,10 +4215,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118787669</v>
+        <v>118787720</v>
       </c>
       <c r="B34" t="n">
-        <v>106776</v>
+        <v>98469</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4241,34 +4231,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220079</v>
+        <v>222295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>716054</v>
+        <v>716046</v>
       </c>
       <c r="R34" t="n">
-        <v>6351534</v>
+        <v>6351830</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4301,6 +4300,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4332,10 +4336,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118787693</v>
+        <v>118787579</v>
       </c>
       <c r="B35" t="n">
-        <v>106776</v>
+        <v>98469</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4348,34 +4352,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220079</v>
+        <v>222295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>716098</v>
+        <v>715987</v>
       </c>
       <c r="R35" t="n">
-        <v>6351710</v>
+        <v>6351753</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4408,6 +4421,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4439,10 +4457,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118787604</v>
+        <v>118787703</v>
       </c>
       <c r="B36" t="n">
-        <v>106120</v>
+        <v>99504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4455,34 +4473,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>222617</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>715937</v>
+        <v>716089</v>
       </c>
       <c r="R36" t="n">
-        <v>6351646</v>
+        <v>6351790</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4528,7 +4555,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4546,10 +4573,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118787633</v>
+        <v>118787777</v>
       </c>
       <c r="B37" t="n">
-        <v>106120</v>
+        <v>42699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4562,34 +4589,53 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>101070</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>716028</v>
+        <v>716078</v>
       </c>
       <c r="R37" t="n">
-        <v>6351513</v>
+        <v>6351809</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4635,7 +4681,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4653,10 +4699,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118787721</v>
+        <v>118787724</v>
       </c>
       <c r="B38" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4669,43 +4715,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716046</v>
+        <v>716048</v>
       </c>
       <c r="R38" t="n">
-        <v>6351830</v>
+        <v>6351840</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4769,10 +4806,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118787649</v>
+        <v>118787673</v>
       </c>
       <c r="B39" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4785,21 +4822,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4809,10 +4846,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715990</v>
+        <v>716097</v>
       </c>
       <c r="R39" t="n">
-        <v>6351309</v>
+        <v>6351540</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4876,10 +4913,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118787576</v>
+        <v>118787751</v>
       </c>
       <c r="B40" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4892,21 +4929,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4916,10 +4953,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716038</v>
+        <v>716069</v>
       </c>
       <c r="R40" t="n">
-        <v>6351750</v>
+        <v>6351918</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4983,10 +5020,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118787725</v>
+        <v>118787734</v>
       </c>
       <c r="B41" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4999,21 +5036,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5023,10 +5060,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716048</v>
+        <v>716068</v>
       </c>
       <c r="R41" t="n">
-        <v>6351840</v>
+        <v>6351879</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5090,10 +5127,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118787680</v>
+        <v>118787580</v>
       </c>
       <c r="B42" t="n">
-        <v>106776</v>
+        <v>103360</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5106,21 +5143,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220079</v>
+        <v>220164</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5130,10 +5167,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716111</v>
+        <v>715987</v>
       </c>
       <c r="R42" t="n">
-        <v>6351576</v>
+        <v>6351753</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5166,11 +5203,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5202,10 +5234,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118787653</v>
+        <v>118787592</v>
       </c>
       <c r="B43" t="n">
-        <v>105495</v>
+        <v>106120</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5214,20 +5246,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5242,13 +5274,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716128</v>
+        <v>715921</v>
       </c>
       <c r="R43" t="n">
-        <v>6351284</v>
+        <v>6351722</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5291,7 +5323,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5309,10 +5341,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118787755</v>
+        <v>118787596</v>
       </c>
       <c r="B44" t="n">
-        <v>105495</v>
+        <v>105736</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5321,20 +5353,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220785</v>
+        <v>221903</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5349,13 +5381,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716067</v>
+        <v>715882</v>
       </c>
       <c r="R44" t="n">
-        <v>6351944</v>
+        <v>6351669</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5385,11 +5417,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5421,10 +5448,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118787637</v>
+        <v>118787735</v>
       </c>
       <c r="B45" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5437,21 +5464,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5461,13 +5488,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715847</v>
+        <v>716068</v>
       </c>
       <c r="R45" t="n">
-        <v>6351378</v>
+        <v>6351879</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5510,7 +5537,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5528,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118787629</v>
+        <v>118787628</v>
       </c>
       <c r="B46" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5544,16 +5571,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5561,26 +5588,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716025</v>
+        <v>715996</v>
       </c>
       <c r="R46" t="n">
-        <v>6351589</v>
+        <v>6351660</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5613,11 +5631,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5649,10 +5662,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118787688</v>
+        <v>118787695</v>
       </c>
       <c r="B47" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5665,16 +5678,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5682,29 +5695,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716083</v>
+        <v>716099</v>
       </c>
       <c r="R47" t="n">
-        <v>6351660</v>
+        <v>6351734</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5734,11 +5738,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5770,10 +5769,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118787668</v>
+        <v>118787590</v>
       </c>
       <c r="B48" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5786,16 +5785,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5810,10 +5809,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716076</v>
+        <v>715935</v>
       </c>
       <c r="R48" t="n">
-        <v>6351474</v>
+        <v>6351703</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5846,11 +5845,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5882,10 +5876,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118787628</v>
+        <v>118787704</v>
       </c>
       <c r="B49" t="n">
-        <v>106120</v>
+        <v>103360</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5898,21 +5892,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5922,10 +5916,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715996</v>
+        <v>716089</v>
       </c>
       <c r="R49" t="n">
-        <v>6351660</v>
+        <v>6351790</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5971,7 +5965,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5989,10 +5983,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118787694</v>
+        <v>118787729</v>
       </c>
       <c r="B50" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6005,21 +5999,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6029,10 +6023,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716098</v>
+        <v>716049</v>
       </c>
       <c r="R50" t="n">
-        <v>6351710</v>
+        <v>6351866</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6096,7 +6090,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118787586</v>
+        <v>118787641</v>
       </c>
       <c r="B51" t="n">
         <v>106776</v>
@@ -6129,20 +6123,29 @@
           <t>(L.) Scop.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715957</v>
+        <v>715886</v>
       </c>
       <c r="R51" t="n">
-        <v>6351748</v>
+        <v>6351326</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6185,7 +6188,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6203,10 +6206,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118787627</v>
+        <v>118787581</v>
       </c>
       <c r="B52" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6219,21 +6222,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6243,10 +6246,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715996</v>
+        <v>715987</v>
       </c>
       <c r="R52" t="n">
-        <v>6351660</v>
+        <v>6351753</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6310,10 +6313,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118787703</v>
+        <v>118787593</v>
       </c>
       <c r="B53" t="n">
-        <v>99504</v>
+        <v>106776</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6326,43 +6329,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222617</v>
+        <v>220079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716089</v>
+        <v>715906</v>
       </c>
       <c r="R53" t="n">
-        <v>6351790</v>
+        <v>6351711</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6408,7 +6402,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6426,10 +6420,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118787695</v>
+        <v>118787637</v>
       </c>
       <c r="B54" t="n">
-        <v>106120</v>
+        <v>106776</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6442,21 +6436,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6466,10 +6460,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716099</v>
+        <v>715847</v>
       </c>
       <c r="R54" t="n">
-        <v>6351734</v>
+        <v>6351378</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6515,7 +6509,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6533,10 +6527,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118787583</v>
+        <v>118787649</v>
       </c>
       <c r="B55" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6549,21 +6543,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6573,10 +6567,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715975</v>
+        <v>715990</v>
       </c>
       <c r="R55" t="n">
-        <v>6351761</v>
+        <v>6351309</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6640,10 +6634,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118787756</v>
+        <v>118787700</v>
       </c>
       <c r="B56" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6656,16 +6650,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6680,13 +6674,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716067</v>
+        <v>716089</v>
       </c>
       <c r="R56" t="n">
-        <v>6351944</v>
+        <v>6351760</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6716,11 +6710,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6752,7 +6741,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118787595</v>
+        <v>118787600</v>
       </c>
       <c r="B57" t="n">
         <v>106120</v>
@@ -6792,10 +6781,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715904</v>
+        <v>715881</v>
       </c>
       <c r="R57" t="n">
-        <v>6351691</v>
+        <v>6351621</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6859,10 +6848,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118787591</v>
+        <v>118787754</v>
       </c>
       <c r="B58" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6875,16 +6864,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6899,10 +6888,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>715935</v>
+        <v>716069</v>
       </c>
       <c r="R58" t="n">
-        <v>6351703</v>
+        <v>6351918</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6966,10 +6955,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118787700</v>
+        <v>118787687</v>
       </c>
       <c r="B59" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6982,16 +6971,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6999,17 +6988,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716089</v>
+        <v>716097</v>
       </c>
       <c r="R59" t="n">
-        <v>6351760</v>
+        <v>6351644</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7044,6 +7042,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7055,7 +7058,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7073,10 +7076,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118787678</v>
+        <v>118787613</v>
       </c>
       <c r="B60" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7089,16 +7092,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7113,10 +7116,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716116</v>
+        <v>715954</v>
       </c>
       <c r="R60" t="n">
-        <v>6351568</v>
+        <v>6351671</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7162,7 +7165,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7180,7 +7183,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118787585</v>
+        <v>118787617</v>
       </c>
       <c r="B61" t="n">
         <v>106120</v>
@@ -7220,10 +7223,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715975</v>
+        <v>715968</v>
       </c>
       <c r="R61" t="n">
-        <v>6351761</v>
+        <v>6351681</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7269,7 +7272,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7287,10 +7290,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118787593</v>
+        <v>118787756</v>
       </c>
       <c r="B62" t="n">
-        <v>106776</v>
+        <v>105736</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7303,21 +7306,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7327,13 +7330,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715906</v>
+        <v>716067</v>
       </c>
       <c r="R62" t="n">
-        <v>6351711</v>
+        <v>6351944</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7363,6 +7366,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7394,10 +7402,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118787580</v>
+        <v>118787755</v>
       </c>
       <c r="B63" t="n">
-        <v>103360</v>
+        <v>105495</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7406,25 +7414,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220164</v>
+        <v>220785</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7434,13 +7442,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715987</v>
+        <v>716067</v>
       </c>
       <c r="R63" t="n">
-        <v>6351753</v>
+        <v>6351944</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7470,6 +7478,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7501,10 +7514,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118787718</v>
+        <v>118787698</v>
       </c>
       <c r="B64" t="n">
-        <v>105736</v>
+        <v>106655</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7517,16 +7530,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7534,17 +7547,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>716046</v>
+        <v>716099</v>
       </c>
       <c r="R64" t="n">
-        <v>6351830</v>
+        <v>6351734</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7608,10 +7630,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118787682</v>
+        <v>118787577</v>
       </c>
       <c r="B65" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7624,16 +7646,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7641,17 +7663,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716105</v>
+        <v>716038</v>
       </c>
       <c r="R65" t="n">
-        <v>6351578</v>
+        <v>6351750</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7715,7 +7746,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787698</v>
+        <v>118787721</v>
       </c>
       <c r="B66" t="n">
         <v>106655</v>
@@ -7750,7 +7781,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7764,10 +7795,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716099</v>
+        <v>716046</v>
       </c>
       <c r="R66" t="n">
-        <v>6351734</v>
+        <v>6351830</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7831,7 +7862,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787751</v>
+        <v>118787586</v>
       </c>
       <c r="B67" t="n">
         <v>106776</v>
@@ -7871,13 +7902,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716069</v>
+        <v>715957</v>
       </c>
       <c r="R67" t="n">
-        <v>6351918</v>
+        <v>6351748</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7938,7 +7969,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787722</v>
+        <v>118787677</v>
       </c>
       <c r="B68" t="n">
         <v>106776</v>
@@ -7978,10 +8009,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>716046</v>
+        <v>716116</v>
       </c>
       <c r="R68" t="n">
-        <v>6351830</v>
+        <v>6351568</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8045,10 +8076,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787622</v>
+        <v>118787731</v>
       </c>
       <c r="B69" t="n">
-        <v>105736</v>
+        <v>106776</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8061,21 +8092,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8085,10 +8116,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715968</v>
+        <v>716063</v>
       </c>
       <c r="R69" t="n">
-        <v>6351681</v>
+        <v>6351869</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8134,7 +8165,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -8152,10 +8183,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787584</v>
+        <v>118787578</v>
       </c>
       <c r="B70" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8168,16 +8199,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8192,10 +8223,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>715975</v>
+        <v>716038</v>
       </c>
       <c r="R70" t="n">
-        <v>6351761</v>
+        <v>6351750</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8259,10 +8290,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787671</v>
+        <v>118787587</v>
       </c>
       <c r="B71" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,16 +8306,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8299,10 +8330,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>716074</v>
+        <v>715957</v>
       </c>
       <c r="R71" t="n">
-        <v>6351539</v>
+        <v>6351748</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8366,7 +8397,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118787713</v>
+        <v>118787753</v>
       </c>
       <c r="B72" t="n">
         <v>106120</v>
@@ -8406,10 +8437,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716068</v>
+        <v>716069</v>
       </c>
       <c r="R72" t="n">
-        <v>6351807</v>
+        <v>6351918</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8473,10 +8504,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118787727</v>
+        <v>118787599</v>
       </c>
       <c r="B73" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8489,16 +8520,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8513,10 +8544,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716051</v>
+        <v>715881</v>
       </c>
       <c r="R73" t="n">
-        <v>6351855</v>
+        <v>6351621</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8580,7 +8611,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118787673</v>
+        <v>118787726</v>
       </c>
       <c r="B74" t="n">
         <v>106776</v>
@@ -8620,10 +8651,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716097</v>
+        <v>716051</v>
       </c>
       <c r="R74" t="n">
-        <v>6351540</v>
+        <v>6351855</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8687,10 +8718,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118787685</v>
+        <v>118787713</v>
       </c>
       <c r="B75" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8703,16 +8734,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8720,26 +8751,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716101</v>
+        <v>716068</v>
       </c>
       <c r="R75" t="n">
-        <v>6351620</v>
+        <v>6351807</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8803,10 +8825,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118787652</v>
+        <v>118787718</v>
       </c>
       <c r="B76" t="n">
-        <v>106655</v>
+        <v>105736</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8819,16 +8841,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -8836,26 +8858,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716032</v>
+        <v>716046</v>
       </c>
       <c r="R76" t="n">
-        <v>6351369</v>
+        <v>6351830</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8919,10 +8932,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118787772</v>
+        <v>118787622</v>
       </c>
       <c r="B77" t="n">
-        <v>42699</v>
+        <v>105736</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8935,53 +8948,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>101070</v>
+        <v>221903</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715921</v>
+        <v>715968</v>
       </c>
       <c r="R77" t="n">
-        <v>6351722</v>
+        <v>6351681</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9024,6 +9018,11 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9040,10 +9039,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118787632</v>
+        <v>118787719</v>
       </c>
       <c r="B78" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9056,21 +9055,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9080,10 +9079,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716028</v>
+        <v>716046</v>
       </c>
       <c r="R78" t="n">
-        <v>6351513</v>
+        <v>6351830</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9147,7 +9146,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118787670</v>
+        <v>118787642</v>
       </c>
       <c r="B79" t="n">
         <v>106776</v>
@@ -9187,10 +9186,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>716074</v>
+        <v>715897</v>
       </c>
       <c r="R79" t="n">
-        <v>6351539</v>
+        <v>6351335</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9236,7 +9235,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9254,10 +9253,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118787643</v>
+        <v>118787629</v>
       </c>
       <c r="B80" t="n">
-        <v>100107</v>
+        <v>106655</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9266,38 +9265,47 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>1865</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>715897</v>
+        <v>716025</v>
       </c>
       <c r="R80" t="n">
-        <v>6351335</v>
+        <v>6351589</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9332,6 +9340,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9343,7 +9356,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9361,10 +9374,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118794857</v>
+        <v>118787652</v>
       </c>
       <c r="B81" t="n">
-        <v>57993</v>
+        <v>106655</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9377,31 +9390,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103055</v>
+        <v>1865</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9410,13 +9423,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715968</v>
+        <v>716032</v>
       </c>
       <c r="R81" t="n">
-        <v>6351687</v>
+        <v>6351369</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9477,10 +9490,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118787726</v>
+        <v>118787752</v>
       </c>
       <c r="B82" t="n">
-        <v>106776</v>
+        <v>103360</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9493,21 +9506,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220079</v>
+        <v>220164</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9517,10 +9530,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716051</v>
+        <v>716069</v>
       </c>
       <c r="R82" t="n">
-        <v>6351855</v>
+        <v>6351918</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9584,7 +9597,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118787639</v>
+        <v>118787730</v>
       </c>
       <c r="B83" t="n">
         <v>106120</v>
@@ -9624,13 +9637,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>715847</v>
+        <v>716049</v>
       </c>
       <c r="R83" t="n">
-        <v>6351378</v>
+        <v>6351866</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9673,7 +9686,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9691,7 +9704,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118787730</v>
+        <v>118787594</v>
       </c>
       <c r="B84" t="n">
         <v>106120</v>
@@ -9731,10 +9744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>716049</v>
+        <v>715906</v>
       </c>
       <c r="R84" t="n">
-        <v>6351866</v>
+        <v>6351711</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9798,7 +9811,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118787594</v>
+        <v>118787633</v>
       </c>
       <c r="B85" t="n">
         <v>106120</v>
@@ -9838,10 +9851,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715906</v>
+        <v>716028</v>
       </c>
       <c r="R85" t="n">
-        <v>6351711</v>
+        <v>6351513</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9905,10 +9918,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118787599</v>
+        <v>118787682</v>
       </c>
       <c r="B86" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9921,16 +9934,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9945,10 +9958,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>715881</v>
+        <v>716105</v>
       </c>
       <c r="R86" t="n">
-        <v>6351621</v>
+        <v>6351578</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10012,10 +10025,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118787577</v>
+        <v>118787585</v>
       </c>
       <c r="B87" t="n">
-        <v>106655</v>
+        <v>106120</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10028,16 +10041,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10045,26 +10058,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>716038</v>
+        <v>715975</v>
       </c>
       <c r="R87" t="n">
-        <v>6351750</v>
+        <v>6351761</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10244,10 +10248,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118787667</v>
+        <v>118787669</v>
       </c>
       <c r="B89" t="n">
-        <v>106655</v>
+        <v>106776</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10260,43 +10264,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>716086</v>
+        <v>716054</v>
       </c>
       <c r="R89" t="n">
-        <v>6351456</v>
+        <v>6351534</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10360,10 +10355,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118787642</v>
+        <v>118787668</v>
       </c>
       <c r="B90" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10376,21 +10371,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10400,10 +10395,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>715897</v>
+        <v>716076</v>
       </c>
       <c r="R90" t="n">
-        <v>6351335</v>
+        <v>6351474</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10438,6 +10433,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10467,7 +10467,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118787729</v>
+        <v>118787583</v>
       </c>
       <c r="B91" t="n">
         <v>106776</v>
@@ -10507,10 +10507,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>716049</v>
+        <v>715975</v>
       </c>
       <c r="R91" t="n">
-        <v>6351866</v>
+        <v>6351761</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10574,7 +10574,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118787630</v>
+        <v>118787604</v>
       </c>
       <c r="B92" t="n">
         <v>106120</v>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>716025</v>
+        <v>715937</v>
       </c>
       <c r="R92" t="n">
-        <v>6351589</v>
+        <v>6351646</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118787720</v>
+        <v>118787603</v>
       </c>
       <c r="B93" t="n">
-        <v>98469</v>
+        <v>106120</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10697,43 +10697,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222295</v>
+        <v>221849</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>716046</v>
+        <v>715907</v>
       </c>
       <c r="R93" t="n">
-        <v>6351830</v>
+        <v>6351637</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10768,11 +10759,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10784,7 +10770,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10802,10 +10788,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118787588</v>
+        <v>118787584</v>
       </c>
       <c r="B94" t="n">
-        <v>106120</v>
+        <v>105736</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10818,16 +10804,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -10842,10 +10828,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715957</v>
+        <v>715975</v>
       </c>
       <c r="R94" t="n">
-        <v>6351748</v>
+        <v>6351761</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10909,10 +10895,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118787581</v>
+        <v>118787666</v>
       </c>
       <c r="B95" t="n">
-        <v>106120</v>
+        <v>106655</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10925,16 +10911,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10942,17 +10928,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>715987</v>
+        <v>716106</v>
       </c>
       <c r="R95" t="n">
-        <v>6351753</v>
+        <v>6351403</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10985,6 +10980,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11016,10 +11016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118787724</v>
+        <v>118787630</v>
       </c>
       <c r="B96" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11032,21 +11032,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716048</v>
+        <v>716025</v>
       </c>
       <c r="R96" t="n">
-        <v>6351840</v>
+        <v>6351589</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11123,10 +11123,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118787731</v>
+        <v>118787678</v>
       </c>
       <c r="B97" t="n">
-        <v>106776</v>
+        <v>106120</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11139,21 +11139,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716063</v>
+        <v>716116</v>
       </c>
       <c r="R97" t="n">
-        <v>6351869</v>
+        <v>6351568</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11230,10 +11230,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118787712</v>
+        <v>118787725</v>
       </c>
       <c r="B98" t="n">
-        <v>105736</v>
+        <v>106120</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11246,16 +11246,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716068</v>
+        <v>716048</v>
       </c>
       <c r="R98" t="n">
-        <v>6351807</v>
+        <v>6351840</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11337,7 +11337,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787732</v>
+        <v>118787681</v>
       </c>
       <c r="B99" t="n">
         <v>106120</v>
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716063</v>
+        <v>716111</v>
       </c>
       <c r="R99" t="n">
-        <v>6351869</v>
+        <v>6351576</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11444,7 +11444,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787753</v>
+        <v>118787588</v>
       </c>
       <c r="B100" t="n">
         <v>106120</v>
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>716069</v>
+        <v>715957</v>
       </c>
       <c r="R100" t="n">
-        <v>6351918</v>
+        <v>6351748</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11551,7 +11551,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787681</v>
+        <v>118787595</v>
       </c>
       <c r="B101" t="n">
         <v>106120</v>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>716111</v>
+        <v>715904</v>
       </c>
       <c r="R101" t="n">
-        <v>6351576</v>
+        <v>6351691</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118787643</v>
+        <v>118787608</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
+        <v>105743</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,25 +823,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221903</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715897</v>
+        <v>715936</v>
       </c>
       <c r="R3" t="n">
-        <v>6351335</v>
+        <v>6351658</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118794857</v>
+        <v>118787711</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>106127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,46 +934,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>221849</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715968</v>
+        <v>716078</v>
       </c>
       <c r="R4" t="n">
-        <v>6351687</v>
+        <v>6351809</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118787651</v>
+        <v>118787695</v>
       </c>
       <c r="B5" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,16 +1041,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,29 +1058,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716014</v>
+        <v>716099</v>
       </c>
       <c r="R5" t="n">
-        <v>6351361</v>
+        <v>6351734</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1150,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118787684</v>
+        <v>118787629</v>
       </c>
       <c r="B6" t="n">
-        <v>103360</v>
+        <v>106662</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,37 +1148,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220164</v>
+        <v>1865</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716101</v>
+        <v>716025</v>
       </c>
       <c r="R6" t="n">
-        <v>6351620</v>
+        <v>6351589</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1226,6 +1217,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118787632</v>
+        <v>118787673</v>
       </c>
       <c r="B7" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1297,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716028</v>
+        <v>716097</v>
       </c>
       <c r="R7" t="n">
-        <v>6351513</v>
+        <v>6351540</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1364,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787639</v>
+        <v>118787686</v>
       </c>
       <c r="B8" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1404,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715847</v>
+        <v>716097</v>
       </c>
       <c r="R8" t="n">
-        <v>6351378</v>
+        <v>6351644</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,7 +1449,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1471,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787727</v>
+        <v>118787722</v>
       </c>
       <c r="B9" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,21 +1483,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716051</v>
+        <v>716046</v>
       </c>
       <c r="R9" t="n">
-        <v>6351855</v>
+        <v>6351830</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1578,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787608</v>
+        <v>118787712</v>
       </c>
       <c r="B10" t="n">
-        <v>105736</v>
+        <v>105743</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>715936</v>
+        <v>716068</v>
       </c>
       <c r="R10" t="n">
-        <v>6351658</v>
+        <v>6351807</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,7 +1663,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1685,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787712</v>
+        <v>118787628</v>
       </c>
       <c r="B11" t="n">
-        <v>105736</v>
+        <v>106127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1701,16 +1697,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1725,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716068</v>
+        <v>715996</v>
       </c>
       <c r="R11" t="n">
-        <v>6351807</v>
+        <v>6351660</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,10 +1788,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787686</v>
+        <v>118787580</v>
       </c>
       <c r="B12" t="n">
-        <v>106776</v>
+        <v>103367</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1808,21 +1804,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220079</v>
+        <v>220164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1832,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716097</v>
+        <v>715987</v>
       </c>
       <c r="R12" t="n">
-        <v>6351644</v>
+        <v>6351753</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1899,10 +1895,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118787670</v>
+        <v>118787688</v>
       </c>
       <c r="B13" t="n">
-        <v>106776</v>
+        <v>106662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1915,34 +1911,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716074</v>
+        <v>716083</v>
       </c>
       <c r="R13" t="n">
-        <v>6351539</v>
+        <v>6351660</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1975,6 +1980,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118787711</v>
+        <v>118787705</v>
       </c>
       <c r="B14" t="n">
-        <v>106120</v>
+        <v>106662</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2022,16 +2032,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2039,17 +2049,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716078</v>
+        <v>716089</v>
       </c>
       <c r="R14" t="n">
-        <v>6351809</v>
+        <v>6351790</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2095,7 +2114,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2113,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118787616</v>
+        <v>118787652</v>
       </c>
       <c r="B15" t="n">
-        <v>106120</v>
+        <v>106662</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2129,16 +2148,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2146,20 +2165,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715954</v>
+        <v>716032</v>
       </c>
       <c r="R15" t="n">
-        <v>6351671</v>
+        <v>6351369</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2202,7 +2230,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2220,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118787671</v>
+        <v>118787704</v>
       </c>
       <c r="B16" t="n">
-        <v>106120</v>
+        <v>103367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2236,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716074</v>
+        <v>716089</v>
       </c>
       <c r="R16" t="n">
-        <v>6351539</v>
+        <v>6351790</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2309,7 +2337,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2327,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118787667</v>
+        <v>118787723</v>
       </c>
       <c r="B17" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2343,16 +2371,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2360,26 +2388,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716086</v>
+        <v>716046</v>
       </c>
       <c r="R17" t="n">
-        <v>6351456</v>
+        <v>6351830</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2443,10 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118787685</v>
+        <v>118787751</v>
       </c>
       <c r="B18" t="n">
-        <v>106655</v>
+        <v>106783</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2459,43 +2478,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716101</v>
+        <v>716069</v>
       </c>
       <c r="R18" t="n">
-        <v>6351620</v>
+        <v>6351918</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2559,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118787772</v>
+        <v>118787642</v>
       </c>
       <c r="B19" t="n">
-        <v>42699</v>
+        <v>106783</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,53 +2585,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101070</v>
+        <v>220079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715921</v>
+        <v>715897</v>
       </c>
       <c r="R19" t="n">
-        <v>6351722</v>
+        <v>6351335</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2664,6 +2655,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2680,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118787693</v>
+        <v>118787587</v>
       </c>
       <c r="B20" t="n">
-        <v>106776</v>
+        <v>105743</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2696,21 +2692,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2720,10 +2716,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716098</v>
+        <v>715957</v>
       </c>
       <c r="R20" t="n">
-        <v>6351710</v>
+        <v>6351748</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2787,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118787627</v>
+        <v>118787604</v>
       </c>
       <c r="B21" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2803,21 +2799,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2827,10 +2823,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715996</v>
+        <v>715937</v>
       </c>
       <c r="R21" t="n">
-        <v>6351660</v>
+        <v>6351646</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2876,7 +2872,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2894,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118787732</v>
+        <v>118787681</v>
       </c>
       <c r="B22" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,10 +2930,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716063</v>
+        <v>716111</v>
       </c>
       <c r="R22" t="n">
-        <v>6351869</v>
+        <v>6351576</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3001,10 +2997,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118787650</v>
+        <v>118787609</v>
       </c>
       <c r="B23" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3017,16 +3013,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3034,26 +3030,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716014</v>
+        <v>715936</v>
       </c>
       <c r="R23" t="n">
-        <v>6351357</v>
+        <v>6351658</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3099,7 +3086,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3117,10 +3104,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118787688</v>
+        <v>118787578</v>
       </c>
       <c r="B24" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3133,16 +3120,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3150,26 +3137,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716083</v>
+        <v>716038</v>
       </c>
       <c r="R24" t="n">
-        <v>6351660</v>
+        <v>6351750</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3202,11 +3180,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3238,10 +3211,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118787680</v>
+        <v>118787627</v>
       </c>
       <c r="B25" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3278,10 +3251,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716111</v>
+        <v>715996</v>
       </c>
       <c r="R25" t="n">
-        <v>6351576</v>
+        <v>6351660</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3314,11 +3287,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3350,10 +3318,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118787653</v>
+        <v>118787650</v>
       </c>
       <c r="B26" t="n">
-        <v>105495</v>
+        <v>106662</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3362,20 +3330,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>1865</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3383,20 +3351,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716128</v>
+        <v>716014</v>
       </c>
       <c r="R26" t="n">
-        <v>6351284</v>
+        <v>6351357</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3439,7 +3416,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3457,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118787645</v>
+        <v>118787755</v>
       </c>
       <c r="B27" t="n">
-        <v>105495</v>
+        <v>105502</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,13 +3474,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>715913</v>
+        <v>716067</v>
       </c>
       <c r="R27" t="n">
-        <v>6351320</v>
+        <v>6351944</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,6 +3512,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3546,7 +3528,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3564,10 +3546,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118787733</v>
+        <v>118787735</v>
       </c>
       <c r="B28" t="n">
-        <v>105736</v>
+        <v>106127</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3580,16 +3562,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3671,10 +3653,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118787609</v>
+        <v>118787733</v>
       </c>
       <c r="B29" t="n">
-        <v>106120</v>
+        <v>105743</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3687,16 +3669,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3711,10 +3693,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715936</v>
+        <v>716068</v>
       </c>
       <c r="R29" t="n">
-        <v>6351658</v>
+        <v>6351879</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3760,7 +3742,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3778,10 +3760,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118787722</v>
+        <v>118787693</v>
       </c>
       <c r="B30" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3818,10 +3800,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716046</v>
+        <v>716098</v>
       </c>
       <c r="R30" t="n">
-        <v>6351830</v>
+        <v>6351710</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3885,10 +3867,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118787694</v>
+        <v>118787677</v>
       </c>
       <c r="B31" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3901,21 +3883,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3925,10 +3907,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716098</v>
+        <v>716116</v>
       </c>
       <c r="R31" t="n">
-        <v>6351710</v>
+        <v>6351568</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3992,10 +3974,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118787591</v>
+        <v>118787641</v>
       </c>
       <c r="B32" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4008,34 +3990,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715935</v>
+        <v>715886</v>
       </c>
       <c r="R32" t="n">
-        <v>6351703</v>
+        <v>6351326</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4081,7 +4072,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4099,10 +4090,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118787676</v>
+        <v>118787583</v>
       </c>
       <c r="B33" t="n">
-        <v>106655</v>
+        <v>106783</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4115,43 +4106,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>716116</v>
+        <v>715975</v>
       </c>
       <c r="R33" t="n">
-        <v>6351568</v>
+        <v>6351761</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4215,10 +4197,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118787720</v>
+        <v>118787668</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>106127</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4231,43 +4213,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222295</v>
+        <v>221849</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>716046</v>
+        <v>716076</v>
       </c>
       <c r="R34" t="n">
-        <v>6351830</v>
+        <v>6351474</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4304,7 +4277,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4336,10 +4309,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118787579</v>
+        <v>118787600</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>106127</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4352,43 +4325,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222295</v>
+        <v>221849</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715987</v>
+        <v>715881</v>
       </c>
       <c r="R35" t="n">
-        <v>6351753</v>
+        <v>6351621</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4421,11 +4385,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4457,10 +4416,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118787703</v>
+        <v>118787682</v>
       </c>
       <c r="B36" t="n">
-        <v>99504</v>
+        <v>106127</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4473,43 +4432,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>716089</v>
+        <v>716105</v>
       </c>
       <c r="R36" t="n">
-        <v>6351790</v>
+        <v>6351578</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4555,7 +4505,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4573,10 +4523,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118787777</v>
+        <v>118787585</v>
       </c>
       <c r="B37" t="n">
-        <v>42699</v>
+        <v>106127</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4589,53 +4539,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>101070</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>716078</v>
+        <v>715975</v>
       </c>
       <c r="R37" t="n">
-        <v>6351809</v>
+        <v>6351761</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4681,7 +4612,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4699,10 +4630,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118787724</v>
+        <v>118787713</v>
       </c>
       <c r="B38" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4715,21 +4646,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4739,10 +4670,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716048</v>
+        <v>716068</v>
       </c>
       <c r="R38" t="n">
-        <v>6351840</v>
+        <v>6351807</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4806,10 +4737,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118787673</v>
+        <v>118787581</v>
       </c>
       <c r="B39" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4822,21 +4753,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4846,10 +4777,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716097</v>
+        <v>715987</v>
       </c>
       <c r="R39" t="n">
-        <v>6351540</v>
+        <v>6351753</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4913,10 +4844,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118787751</v>
+        <v>118787653</v>
       </c>
       <c r="B40" t="n">
-        <v>106776</v>
+        <v>105502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4925,25 +4856,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4953,13 +4884,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716069</v>
+        <v>716128</v>
       </c>
       <c r="R40" t="n">
-        <v>6351918</v>
+        <v>6351284</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5002,7 +4933,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5020,10 +4951,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118787734</v>
+        <v>118787698</v>
       </c>
       <c r="B41" t="n">
-        <v>106776</v>
+        <v>106662</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5036,34 +4967,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716068</v>
+        <v>716099</v>
       </c>
       <c r="R41" t="n">
-        <v>6351879</v>
+        <v>6351734</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5127,10 +5067,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118787580</v>
+        <v>118787721</v>
       </c>
       <c r="B42" t="n">
-        <v>103360</v>
+        <v>106662</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5143,34 +5083,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220164</v>
+        <v>1865</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>715987</v>
+        <v>716046</v>
       </c>
       <c r="R42" t="n">
-        <v>6351753</v>
+        <v>6351830</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5234,10 +5183,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118787592</v>
+        <v>118787666</v>
       </c>
       <c r="B43" t="n">
-        <v>106120</v>
+        <v>106662</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5250,16 +5199,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5267,17 +5216,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715921</v>
+        <v>716106</v>
       </c>
       <c r="R43" t="n">
-        <v>6351722</v>
+        <v>6351403</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5310,6 +5268,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5341,10 +5304,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118787596</v>
+        <v>118787772</v>
       </c>
       <c r="B44" t="n">
-        <v>105736</v>
+        <v>42699</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5357,34 +5320,53 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221903</v>
+        <v>101070</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715882</v>
+        <v>715921</v>
       </c>
       <c r="R44" t="n">
-        <v>6351669</v>
+        <v>6351722</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5427,11 +5409,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5448,10 +5425,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118787735</v>
+        <v>118787592</v>
       </c>
       <c r="B45" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5488,10 +5465,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716068</v>
+        <v>715921</v>
       </c>
       <c r="R45" t="n">
-        <v>6351879</v>
+        <v>6351722</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5555,10 +5532,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118787628</v>
+        <v>118787616</v>
       </c>
       <c r="B46" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5595,13 +5572,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715996</v>
+        <v>715954</v>
       </c>
       <c r="R46" t="n">
-        <v>6351660</v>
+        <v>6351671</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5644,7 +5621,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5662,10 +5639,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118787695</v>
+        <v>118787729</v>
       </c>
       <c r="B47" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5678,21 +5655,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5702,13 +5679,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716099</v>
+        <v>716049</v>
       </c>
       <c r="R47" t="n">
-        <v>6351734</v>
+        <v>6351866</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5769,10 +5746,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118787590</v>
+        <v>118787670</v>
       </c>
       <c r="B48" t="n">
-        <v>105736</v>
+        <v>106783</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5785,21 +5762,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5809,10 +5786,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>715935</v>
+        <v>716074</v>
       </c>
       <c r="R48" t="n">
-        <v>6351703</v>
+        <v>6351539</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5876,10 +5853,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118787704</v>
+        <v>118787643</v>
       </c>
       <c r="B49" t="n">
-        <v>103360</v>
+        <v>100114</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5888,25 +5865,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220164</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5916,10 +5893,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716089</v>
+        <v>715897</v>
       </c>
       <c r="R49" t="n">
-        <v>6351790</v>
+        <v>6351335</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5965,7 +5942,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5983,10 +5960,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118787729</v>
+        <v>118787718</v>
       </c>
       <c r="B50" t="n">
-        <v>106776</v>
+        <v>105743</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5999,21 +5976,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6023,10 +6000,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716049</v>
+        <v>716046</v>
       </c>
       <c r="R50" t="n">
-        <v>6351866</v>
+        <v>6351830</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6090,10 +6067,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118787641</v>
+        <v>118787622</v>
       </c>
       <c r="B51" t="n">
-        <v>106776</v>
+        <v>105743</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6106,43 +6083,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715886</v>
+        <v>715968</v>
       </c>
       <c r="R51" t="n">
-        <v>6351326</v>
+        <v>6351681</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6188,7 +6156,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6206,10 +6174,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118787581</v>
+        <v>118787595</v>
       </c>
       <c r="B52" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6246,10 +6214,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715987</v>
+        <v>715904</v>
       </c>
       <c r="R52" t="n">
-        <v>6351753</v>
+        <v>6351691</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6313,10 +6281,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118787593</v>
+        <v>118787700</v>
       </c>
       <c r="B53" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6329,21 +6297,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6353,10 +6321,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>715906</v>
+        <v>716089</v>
       </c>
       <c r="R53" t="n">
-        <v>6351711</v>
+        <v>6351760</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6420,10 +6388,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118787637</v>
+        <v>118787584</v>
       </c>
       <c r="B54" t="n">
-        <v>106776</v>
+        <v>105743</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6436,21 +6404,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6460,13 +6428,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715847</v>
+        <v>715975</v>
       </c>
       <c r="R54" t="n">
-        <v>6351378</v>
+        <v>6351761</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6509,7 +6477,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6527,10 +6495,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118787649</v>
+        <v>118787586</v>
       </c>
       <c r="B55" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6543,21 +6511,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6567,13 +6535,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715990</v>
+        <v>715957</v>
       </c>
       <c r="R55" t="n">
-        <v>6351309</v>
+        <v>6351748</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6634,10 +6602,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118787700</v>
+        <v>118787593</v>
       </c>
       <c r="B56" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6650,21 +6618,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6674,10 +6642,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716089</v>
+        <v>715906</v>
       </c>
       <c r="R56" t="n">
-        <v>6351760</v>
+        <v>6351711</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6741,10 +6709,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118787600</v>
+        <v>118787579</v>
       </c>
       <c r="B57" t="n">
-        <v>106120</v>
+        <v>98476</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6757,34 +6725,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221849</v>
+        <v>222295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715881</v>
+        <v>715987</v>
       </c>
       <c r="R57" t="n">
-        <v>6351621</v>
+        <v>6351753</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6817,6 +6794,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6848,10 +6830,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118787754</v>
+        <v>118787671</v>
       </c>
       <c r="B58" t="n">
-        <v>105736</v>
+        <v>106127</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6864,16 +6846,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6888,10 +6870,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716069</v>
+        <v>716074</v>
       </c>
       <c r="R58" t="n">
-        <v>6351918</v>
+        <v>6351539</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6955,10 +6937,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118787687</v>
+        <v>118787577</v>
       </c>
       <c r="B59" t="n">
-        <v>106655</v>
+        <v>106662</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6990,7 +6972,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7004,10 +6986,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716097</v>
+        <v>716038</v>
       </c>
       <c r="R59" t="n">
-        <v>6351644</v>
+        <v>6351750</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7042,11 +7024,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7058,7 +7035,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7076,10 +7053,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118787613</v>
+        <v>118787680</v>
       </c>
       <c r="B60" t="n">
-        <v>105736</v>
+        <v>106783</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7092,21 +7069,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7116,10 +7093,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>715954</v>
+        <v>716111</v>
       </c>
       <c r="R60" t="n">
-        <v>6351671</v>
+        <v>6351576</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7154,6 +7131,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7165,7 +7147,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7183,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118787617</v>
+        <v>118787669</v>
       </c>
       <c r="B61" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7199,21 +7181,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7223,10 +7205,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>715968</v>
+        <v>716054</v>
       </c>
       <c r="R61" t="n">
-        <v>6351681</v>
+        <v>6351534</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7272,7 +7254,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7290,10 +7272,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118787756</v>
+        <v>118787645</v>
       </c>
       <c r="B62" t="n">
-        <v>105736</v>
+        <v>105502</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7302,20 +7284,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221903</v>
+        <v>220785</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7330,13 +7312,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>716067</v>
+        <v>715913</v>
       </c>
       <c r="R62" t="n">
-        <v>6351944</v>
+        <v>6351320</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7368,11 +7350,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7384,7 +7361,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7402,10 +7379,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118787755</v>
+        <v>118787684</v>
       </c>
       <c r="B63" t="n">
-        <v>105495</v>
+        <v>103367</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7414,25 +7391,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7442,10 +7419,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716067</v>
+        <v>716101</v>
       </c>
       <c r="R63" t="n">
-        <v>6351944</v>
+        <v>6351620</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7478,11 +7455,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7514,10 +7486,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118787698</v>
+        <v>118787753</v>
       </c>
       <c r="B64" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7530,16 +7502,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7547,26 +7519,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>716099</v>
+        <v>716069</v>
       </c>
       <c r="R64" t="n">
-        <v>6351734</v>
+        <v>6351918</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7630,10 +7593,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118787577</v>
+        <v>118787725</v>
       </c>
       <c r="B65" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7646,16 +7609,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7663,26 +7626,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716038</v>
+        <v>716048</v>
       </c>
       <c r="R65" t="n">
-        <v>6351750</v>
+        <v>6351840</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7746,10 +7700,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787721</v>
+        <v>118787703</v>
       </c>
       <c r="B66" t="n">
-        <v>106655</v>
+        <v>99511</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7762,26 +7716,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1865</v>
+        <v>222617</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) H. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7795,10 +7749,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716046</v>
+        <v>716089</v>
       </c>
       <c r="R66" t="n">
-        <v>6351830</v>
+        <v>6351790</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7844,7 +7798,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7862,10 +7816,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787586</v>
+        <v>118787633</v>
       </c>
       <c r="B67" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7878,21 +7832,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7902,13 +7856,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>715957</v>
+        <v>716028</v>
       </c>
       <c r="R67" t="n">
-        <v>6351748</v>
+        <v>6351513</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7969,10 +7923,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787677</v>
+        <v>118787613</v>
       </c>
       <c r="B68" t="n">
-        <v>106776</v>
+        <v>105743</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7985,21 +7939,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8009,10 +7963,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>716116</v>
+        <v>715954</v>
       </c>
       <c r="R68" t="n">
-        <v>6351568</v>
+        <v>6351671</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8058,7 +8012,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8076,10 +8030,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787731</v>
+        <v>118787726</v>
       </c>
       <c r="B69" t="n">
-        <v>106776</v>
+        <v>106783</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8116,10 +8070,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716063</v>
+        <v>716051</v>
       </c>
       <c r="R69" t="n">
-        <v>6351869</v>
+        <v>6351855</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8183,10 +8137,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787578</v>
+        <v>118787752</v>
       </c>
       <c r="B70" t="n">
-        <v>106120</v>
+        <v>103367</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8199,21 +8153,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8223,10 +8177,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716038</v>
+        <v>716069</v>
       </c>
       <c r="R70" t="n">
-        <v>6351750</v>
+        <v>6351918</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8290,10 +8244,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787587</v>
+        <v>118787630</v>
       </c>
       <c r="B71" t="n">
-        <v>105736</v>
+        <v>106127</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8306,16 +8260,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8330,10 +8284,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715957</v>
+        <v>716025</v>
       </c>
       <c r="R71" t="n">
-        <v>6351748</v>
+        <v>6351589</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8397,10 +8351,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118787753</v>
+        <v>118787777</v>
       </c>
       <c r="B72" t="n">
-        <v>106120</v>
+        <v>42699</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8413,34 +8367,53 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221849</v>
+        <v>101070</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716069</v>
+        <v>716078</v>
       </c>
       <c r="R72" t="n">
-        <v>6351918</v>
+        <v>6351809</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8486,7 +8459,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8504,10 +8477,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118787599</v>
+        <v>118787649</v>
       </c>
       <c r="B73" t="n">
-        <v>105736</v>
+        <v>106127</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8520,16 +8493,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8544,10 +8517,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715881</v>
+        <v>715990</v>
       </c>
       <c r="R73" t="n">
-        <v>6351621</v>
+        <v>6351309</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8611,10 +8584,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118787726</v>
+        <v>118787727</v>
       </c>
       <c r="B74" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8627,21 +8600,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8718,10 +8691,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118787713</v>
+        <v>118787754</v>
       </c>
       <c r="B75" t="n">
-        <v>106120</v>
+        <v>105743</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8734,16 +8707,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -8758,10 +8731,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716068</v>
+        <v>716069</v>
       </c>
       <c r="R75" t="n">
-        <v>6351807</v>
+        <v>6351918</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8825,10 +8798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118787718</v>
+        <v>118787599</v>
       </c>
       <c r="B76" t="n">
-        <v>105736</v>
+        <v>105743</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8865,10 +8838,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716046</v>
+        <v>715881</v>
       </c>
       <c r="R76" t="n">
-        <v>6351830</v>
+        <v>6351621</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8932,10 +8905,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118787622</v>
+        <v>118787676</v>
       </c>
       <c r="B77" t="n">
-        <v>105736</v>
+        <v>106662</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8948,16 +8921,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8965,17 +8938,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715968</v>
+        <v>716116</v>
       </c>
       <c r="R77" t="n">
-        <v>6351681</v>
+        <v>6351568</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9021,7 +9003,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9039,10 +9021,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118787719</v>
+        <v>118787731</v>
       </c>
       <c r="B78" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9055,21 +9037,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9079,10 +9061,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716046</v>
+        <v>716063</v>
       </c>
       <c r="R78" t="n">
-        <v>6351830</v>
+        <v>6351869</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9146,10 +9128,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118787642</v>
+        <v>118787732</v>
       </c>
       <c r="B79" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9162,21 +9144,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9186,10 +9168,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>715897</v>
+        <v>716063</v>
       </c>
       <c r="R79" t="n">
-        <v>6351335</v>
+        <v>6351869</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9235,7 +9217,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9253,10 +9235,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118787629</v>
+        <v>118787687</v>
       </c>
       <c r="B80" t="n">
-        <v>106655</v>
+        <v>106662</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9288,7 +9270,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -9302,10 +9284,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>716025</v>
+        <v>716097</v>
       </c>
       <c r="R80" t="n">
-        <v>6351589</v>
+        <v>6351644</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9342,7 +9324,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9356,7 +9338,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9374,10 +9356,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118787652</v>
+        <v>118787685</v>
       </c>
       <c r="B81" t="n">
-        <v>106655</v>
+        <v>106662</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9409,7 +9391,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9423,10 +9405,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>716032</v>
+        <v>716101</v>
       </c>
       <c r="R81" t="n">
-        <v>6351369</v>
+        <v>6351620</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9490,10 +9472,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118787752</v>
+        <v>118787591</v>
       </c>
       <c r="B82" t="n">
-        <v>103360</v>
+        <v>106127</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9506,21 +9488,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9530,10 +9512,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716069</v>
+        <v>715935</v>
       </c>
       <c r="R82" t="n">
-        <v>6351918</v>
+        <v>6351703</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9597,10 +9579,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118787730</v>
+        <v>118787734</v>
       </c>
       <c r="B83" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9613,21 +9595,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9637,10 +9619,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>716049</v>
+        <v>716068</v>
       </c>
       <c r="R83" t="n">
-        <v>6351866</v>
+        <v>6351879</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9704,10 +9686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118787594</v>
+        <v>118787720</v>
       </c>
       <c r="B84" t="n">
-        <v>106120</v>
+        <v>98476</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9720,34 +9702,43 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221849</v>
+        <v>222295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715906</v>
+        <v>716046</v>
       </c>
       <c r="R84" t="n">
-        <v>6351711</v>
+        <v>6351830</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9780,6 +9771,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9811,10 +9807,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118787633</v>
+        <v>118787596</v>
       </c>
       <c r="B85" t="n">
-        <v>106120</v>
+        <v>105743</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9827,16 +9823,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9851,10 +9847,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>716028</v>
+        <v>715882</v>
       </c>
       <c r="R85" t="n">
-        <v>6351513</v>
+        <v>6351669</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9918,10 +9914,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118787682</v>
+        <v>118787678</v>
       </c>
       <c r="B86" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9958,10 +9954,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>716105</v>
+        <v>716116</v>
       </c>
       <c r="R86" t="n">
-        <v>6351578</v>
+        <v>6351568</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10025,10 +10021,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118787585</v>
+        <v>118787730</v>
       </c>
       <c r="B87" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10065,10 +10061,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715975</v>
+        <v>716049</v>
       </c>
       <c r="R87" t="n">
-        <v>6351761</v>
+        <v>6351866</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10132,10 +10128,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118787705</v>
+        <v>118787603</v>
       </c>
       <c r="B88" t="n">
-        <v>106655</v>
+        <v>106127</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10148,16 +10144,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10165,26 +10161,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>716089</v>
+        <v>715907</v>
       </c>
       <c r="R88" t="n">
-        <v>6351790</v>
+        <v>6351637</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10230,7 +10217,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10248,10 +10235,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118787669</v>
+        <v>118787588</v>
       </c>
       <c r="B89" t="n">
-        <v>106776</v>
+        <v>106127</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10264,21 +10251,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10288,10 +10275,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>716054</v>
+        <v>715957</v>
       </c>
       <c r="R89" t="n">
-        <v>6351534</v>
+        <v>6351748</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10355,10 +10342,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118787668</v>
+        <v>118787694</v>
       </c>
       <c r="B90" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10395,10 +10382,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>716076</v>
+        <v>716098</v>
       </c>
       <c r="R90" t="n">
-        <v>6351474</v>
+        <v>6351710</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10431,11 +10418,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10467,10 +10449,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118787583</v>
+        <v>118794857</v>
       </c>
       <c r="B91" t="n">
-        <v>106776</v>
+        <v>57993</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10483,37 +10465,46 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220079</v>
+        <v>103055</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715975</v>
+        <v>715968</v>
       </c>
       <c r="R91" t="n">
-        <v>6351761</v>
+        <v>6351687</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10574,10 +10565,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118787604</v>
+        <v>118787639</v>
       </c>
       <c r="B92" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10614,13 +10605,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715937</v>
+        <v>715847</v>
       </c>
       <c r="R92" t="n">
-        <v>6351646</v>
+        <v>6351378</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10663,7 +10654,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10681,10 +10672,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118787603</v>
+        <v>118787632</v>
       </c>
       <c r="B93" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10697,21 +10688,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10721,10 +10712,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>715907</v>
+        <v>716028</v>
       </c>
       <c r="R93" t="n">
-        <v>6351637</v>
+        <v>6351513</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10770,7 +10761,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10788,10 +10779,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118787584</v>
+        <v>118787590</v>
       </c>
       <c r="B94" t="n">
-        <v>105736</v>
+        <v>105743</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10828,10 +10819,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715975</v>
+        <v>715935</v>
       </c>
       <c r="R94" t="n">
-        <v>6351761</v>
+        <v>6351703</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10895,10 +10886,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118787666</v>
+        <v>118787667</v>
       </c>
       <c r="B95" t="n">
-        <v>106655</v>
+        <v>106662</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10930,7 +10921,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10944,10 +10935,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716106</v>
+        <v>716086</v>
       </c>
       <c r="R95" t="n">
-        <v>6351403</v>
+        <v>6351456</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10980,11 +10971,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11016,10 +11002,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118787630</v>
+        <v>118787651</v>
       </c>
       <c r="B96" t="n">
-        <v>106120</v>
+        <v>106662</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11032,16 +11018,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -11049,17 +11035,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716025</v>
+        <v>716014</v>
       </c>
       <c r="R96" t="n">
-        <v>6351589</v>
+        <v>6351361</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11123,10 +11118,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118787678</v>
+        <v>118787594</v>
       </c>
       <c r="B97" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11163,10 +11158,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716116</v>
+        <v>715906</v>
       </c>
       <c r="R97" t="n">
-        <v>6351568</v>
+        <v>6351711</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11230,10 +11225,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118787725</v>
+        <v>118787617</v>
       </c>
       <c r="B98" t="n">
-        <v>106120</v>
+        <v>106127</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11270,10 +11265,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716048</v>
+        <v>715968</v>
       </c>
       <c r="R98" t="n">
-        <v>6351840</v>
+        <v>6351681</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11319,7 +11314,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11337,10 +11332,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787681</v>
+        <v>118787756</v>
       </c>
       <c r="B99" t="n">
-        <v>106120</v>
+        <v>105743</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11353,16 +11348,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11377,13 +11372,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716111</v>
+        <v>716067</v>
       </c>
       <c r="R99" t="n">
-        <v>6351576</v>
+        <v>6351944</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11413,6 +11408,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11444,10 +11444,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787588</v>
+        <v>118787724</v>
       </c>
       <c r="B100" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11460,21 +11460,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715957</v>
+        <v>716048</v>
       </c>
       <c r="R100" t="n">
-        <v>6351748</v>
+        <v>6351840</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11551,10 +11551,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787595</v>
+        <v>118787637</v>
       </c>
       <c r="B101" t="n">
-        <v>106120</v>
+        <v>106783</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11567,21 +11567,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715904</v>
+        <v>715847</v>
       </c>
       <c r="R101" t="n">
-        <v>6351691</v>
+        <v>6351378</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118787608</v>
+        <v>118787711</v>
       </c>
       <c r="B3" t="n">
-        <v>105743</v>
+        <v>106127</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,16 +827,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715936</v>
+        <v>716078</v>
       </c>
       <c r="R3" t="n">
-        <v>6351658</v>
+        <v>6351809</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118787711</v>
+        <v>118787608</v>
       </c>
       <c r="B4" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716078</v>
+        <v>715936</v>
       </c>
       <c r="R4" t="n">
-        <v>6351809</v>
+        <v>6351658</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118787704</v>
+        <v>118787723</v>
       </c>
       <c r="B16" t="n">
-        <v>103367</v>
+        <v>106127</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716089</v>
+        <v>716046</v>
       </c>
       <c r="R16" t="n">
-        <v>6351790</v>
+        <v>6351830</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118787723</v>
+        <v>118787704</v>
       </c>
       <c r="B17" t="n">
-        <v>106127</v>
+        <v>103367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716046</v>
+        <v>716089</v>
       </c>
       <c r="R17" t="n">
-        <v>6351830</v>
+        <v>6351790</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -7379,10 +7379,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118787684</v>
+        <v>118787753</v>
       </c>
       <c r="B63" t="n">
-        <v>103367</v>
+        <v>106127</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7395,21 +7395,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7419,13 +7419,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716101</v>
+        <v>716069</v>
       </c>
       <c r="R63" t="n">
-        <v>6351620</v>
+        <v>6351918</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7486,10 +7486,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118787753</v>
+        <v>118787684</v>
       </c>
       <c r="B64" t="n">
-        <v>106127</v>
+        <v>103367</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7502,21 +7502,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7526,13 +7526,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>716069</v>
+        <v>716101</v>
       </c>
       <c r="R64" t="n">
-        <v>6351918</v>
+        <v>6351620</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7700,10 +7700,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787703</v>
+        <v>118787630</v>
       </c>
       <c r="B66" t="n">
-        <v>99511</v>
+        <v>106127</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7716,43 +7716,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716089</v>
+        <v>716025</v>
       </c>
       <c r="R66" t="n">
-        <v>6351790</v>
+        <v>6351589</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7798,7 +7789,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7816,10 +7807,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787633</v>
+        <v>118787726</v>
       </c>
       <c r="B67" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7832,21 +7823,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7856,10 +7847,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716028</v>
+        <v>716051</v>
       </c>
       <c r="R67" t="n">
-        <v>6351513</v>
+        <v>6351855</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7923,10 +7914,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787613</v>
+        <v>118787752</v>
       </c>
       <c r="B68" t="n">
-        <v>105743</v>
+        <v>103367</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7939,21 +7930,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221903</v>
+        <v>220164</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7963,10 +7954,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715954</v>
+        <v>716069</v>
       </c>
       <c r="R68" t="n">
-        <v>6351671</v>
+        <v>6351918</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8012,7 +8003,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8030,10 +8021,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787726</v>
+        <v>118787633</v>
       </c>
       <c r="B69" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8046,21 +8037,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8070,10 +8061,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716051</v>
+        <v>716028</v>
       </c>
       <c r="R69" t="n">
-        <v>6351855</v>
+        <v>6351513</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8137,10 +8128,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787752</v>
+        <v>118787703</v>
       </c>
       <c r="B70" t="n">
-        <v>103367</v>
+        <v>99511</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8153,34 +8144,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220164</v>
+        <v>222617</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716069</v>
+        <v>716089</v>
       </c>
       <c r="R70" t="n">
-        <v>6351918</v>
+        <v>6351790</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8244,10 +8244,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787630</v>
+        <v>118787613</v>
       </c>
       <c r="B71" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8260,16 +8260,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>716025</v>
+        <v>715954</v>
       </c>
       <c r="R71" t="n">
-        <v>6351589</v>
+        <v>6351671</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118787777</v>
+        <v>118787732</v>
       </c>
       <c r="B72" t="n">
-        <v>42699</v>
+        <v>106127</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8367,53 +8367,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>101070</v>
+        <v>221849</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716078</v>
+        <v>716063</v>
       </c>
       <c r="R72" t="n">
-        <v>6351809</v>
+        <v>6351869</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8459,7 +8440,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8477,10 +8458,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118787649</v>
+        <v>118787676</v>
       </c>
       <c r="B73" t="n">
-        <v>106127</v>
+        <v>106662</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8493,16 +8474,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8510,17 +8491,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>715990</v>
+        <v>716116</v>
       </c>
       <c r="R73" t="n">
-        <v>6351309</v>
+        <v>6351568</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8584,10 +8574,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118787727</v>
+        <v>118787731</v>
       </c>
       <c r="B74" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8600,21 +8590,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8624,10 +8614,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716051</v>
+        <v>716063</v>
       </c>
       <c r="R74" t="n">
-        <v>6351855</v>
+        <v>6351869</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8691,10 +8681,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118787754</v>
+        <v>118787777</v>
       </c>
       <c r="B75" t="n">
-        <v>105743</v>
+        <v>42699</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8707,34 +8697,53 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221903</v>
+        <v>101070</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716069</v>
+        <v>716078</v>
       </c>
       <c r="R75" t="n">
-        <v>6351918</v>
+        <v>6351809</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8780,7 +8789,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8798,7 +8807,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118787599</v>
+        <v>118787754</v>
       </c>
       <c r="B76" t="n">
         <v>105743</v>
@@ -8838,10 +8847,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>715881</v>
+        <v>716069</v>
       </c>
       <c r="R76" t="n">
-        <v>6351621</v>
+        <v>6351918</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8905,10 +8914,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118787676</v>
+        <v>118787599</v>
       </c>
       <c r="B77" t="n">
-        <v>106662</v>
+        <v>105743</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8921,16 +8930,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8938,26 +8947,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>716116</v>
+        <v>715881</v>
       </c>
       <c r="R77" t="n">
-        <v>6351568</v>
+        <v>6351621</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9021,10 +9021,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118787731</v>
+        <v>118787649</v>
       </c>
       <c r="B78" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9037,21 +9037,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716063</v>
+        <v>715990</v>
       </c>
       <c r="R78" t="n">
-        <v>6351869</v>
+        <v>6351309</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9128,7 +9128,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118787732</v>
+        <v>118787727</v>
       </c>
       <c r="B79" t="n">
         <v>106127</v>
@@ -9168,10 +9168,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>716063</v>
+        <v>716051</v>
       </c>
       <c r="R79" t="n">
-        <v>6351869</v>
+        <v>6351855</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -11002,10 +11002,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118787651</v>
+        <v>118787724</v>
       </c>
       <c r="B96" t="n">
-        <v>106662</v>
+        <v>106783</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11018,43 +11018,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716014</v>
+        <v>716048</v>
       </c>
       <c r="R96" t="n">
-        <v>6351361</v>
+        <v>6351840</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11118,10 +11109,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118787594</v>
+        <v>118787637</v>
       </c>
       <c r="B97" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11134,21 +11125,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11158,13 +11149,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715906</v>
+        <v>715847</v>
       </c>
       <c r="R97" t="n">
-        <v>6351711</v>
+        <v>6351378</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11207,7 +11198,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11225,10 +11216,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118787617</v>
+        <v>118787756</v>
       </c>
       <c r="B98" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11241,16 +11232,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11265,13 +11256,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>715968</v>
+        <v>716067</v>
       </c>
       <c r="R98" t="n">
-        <v>6351681</v>
+        <v>6351944</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11303,6 +11294,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11314,7 +11310,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11332,10 +11328,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787756</v>
+        <v>118787594</v>
       </c>
       <c r="B99" t="n">
-        <v>105743</v>
+        <v>106127</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11348,16 +11344,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11372,13 +11368,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716067</v>
+        <v>715906</v>
       </c>
       <c r="R99" t="n">
-        <v>6351944</v>
+        <v>6351711</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11408,11 +11404,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11444,10 +11435,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787724</v>
+        <v>118787617</v>
       </c>
       <c r="B100" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11460,21 +11451,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11484,10 +11475,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>716048</v>
+        <v>715968</v>
       </c>
       <c r="R100" t="n">
-        <v>6351840</v>
+        <v>6351681</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11533,7 +11524,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11551,10 +11542,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787637</v>
+        <v>118787651</v>
       </c>
       <c r="B101" t="n">
-        <v>106783</v>
+        <v>106662</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11567,37 +11558,46 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>715847</v>
+        <v>716014</v>
       </c>
       <c r="R101" t="n">
-        <v>6351378</v>
+        <v>6351361</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -811,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118787711</v>
+        <v>118787642</v>
       </c>
       <c r="B3" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,21 +827,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716078</v>
+        <v>715897</v>
       </c>
       <c r="R3" t="n">
-        <v>6351809</v>
+        <v>6351335</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118787608</v>
+        <v>118787613</v>
       </c>
       <c r="B4" t="n">
         <v>105743</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>715936</v>
+        <v>715954</v>
       </c>
       <c r="R4" t="n">
-        <v>6351658</v>
+        <v>6351671</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118787695</v>
+        <v>118787581</v>
       </c>
       <c r="B5" t="n">
         <v>106127</v>
@@ -1065,13 +1065,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716099</v>
+        <v>715987</v>
       </c>
       <c r="R5" t="n">
-        <v>6351734</v>
+        <v>6351753</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118787629</v>
+        <v>118787666</v>
       </c>
       <c r="B6" t="n">
         <v>106662</v>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716025</v>
+        <v>716106</v>
       </c>
       <c r="R6" t="n">
-        <v>6351589</v>
+        <v>6351403</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118787673</v>
+        <v>118787698</v>
       </c>
       <c r="B7" t="n">
-        <v>106783</v>
+        <v>106662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,34 +1269,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716097</v>
+        <v>716099</v>
       </c>
       <c r="R7" t="n">
-        <v>6351540</v>
+        <v>6351734</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1360,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787686</v>
+        <v>118787680</v>
       </c>
       <c r="B8" t="n">
         <v>106783</v>
@@ -1400,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716097</v>
+        <v>716111</v>
       </c>
       <c r="R8" t="n">
-        <v>6351644</v>
+        <v>6351576</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1436,6 +1445,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787722</v>
+        <v>118787724</v>
       </c>
       <c r="B9" t="n">
         <v>106783</v>
@@ -1507,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716046</v>
+        <v>716048</v>
       </c>
       <c r="R9" t="n">
-        <v>6351830</v>
+        <v>6351840</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1574,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787712</v>
+        <v>118787731</v>
       </c>
       <c r="B10" t="n">
-        <v>105743</v>
+        <v>106783</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,21 +1604,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716068</v>
+        <v>716063</v>
       </c>
       <c r="R10" t="n">
-        <v>6351807</v>
+        <v>6351869</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1681,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787628</v>
+        <v>118787722</v>
       </c>
       <c r="B11" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1697,21 +1711,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1721,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>715996</v>
+        <v>716046</v>
       </c>
       <c r="R11" t="n">
-        <v>6351660</v>
+        <v>6351830</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1788,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787580</v>
+        <v>118794857</v>
       </c>
       <c r="B12" t="n">
-        <v>103367</v>
+        <v>57993</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1804,37 +1818,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220164</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>715987</v>
+        <v>715968</v>
       </c>
       <c r="R12" t="n">
-        <v>6351753</v>
+        <v>6351687</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1895,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118787688</v>
+        <v>118787576</v>
       </c>
       <c r="B13" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1911,16 +1934,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1928,26 +1951,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716083</v>
+        <v>716038</v>
       </c>
       <c r="R13" t="n">
-        <v>6351660</v>
+        <v>6351750</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1980,11 +1994,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,10 +2025,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118787705</v>
+        <v>118787700</v>
       </c>
       <c r="B14" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2032,16 +2041,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2049,16 +2058,7 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
@@ -2068,7 +2068,7 @@
         <v>716089</v>
       </c>
       <c r="R14" t="n">
-        <v>6351790</v>
+        <v>6351760</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118787652</v>
+        <v>118787730</v>
       </c>
       <c r="B15" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,16 +2148,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2165,26 +2165,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716032</v>
+        <v>716049</v>
       </c>
       <c r="R15" t="n">
-        <v>6351369</v>
+        <v>6351866</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,7 +2239,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118787723</v>
+        <v>118787585</v>
       </c>
       <c r="B16" t="n">
         <v>106127</v>
@@ -2288,10 +2279,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716046</v>
+        <v>715975</v>
       </c>
       <c r="R16" t="n">
-        <v>6351830</v>
+        <v>6351761</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,10 +2346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118787704</v>
+        <v>118787609</v>
       </c>
       <c r="B17" t="n">
-        <v>103367</v>
+        <v>106127</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2362,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2386,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716089</v>
+        <v>715936</v>
       </c>
       <c r="R17" t="n">
-        <v>6351790</v>
+        <v>6351658</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2444,7 +2435,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2462,10 +2453,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118787751</v>
+        <v>118787713</v>
       </c>
       <c r="B18" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2478,21 +2469,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2493,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716069</v>
+        <v>716068</v>
       </c>
       <c r="R18" t="n">
-        <v>6351918</v>
+        <v>6351807</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118787642</v>
+        <v>118787584</v>
       </c>
       <c r="B19" t="n">
-        <v>106783</v>
+        <v>105743</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2585,21 +2576,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2609,10 +2600,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>715897</v>
+        <v>715975</v>
       </c>
       <c r="R19" t="n">
-        <v>6351335</v>
+        <v>6351761</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2658,7 +2649,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2676,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118787587</v>
+        <v>118787695</v>
       </c>
       <c r="B20" t="n">
-        <v>105743</v>
+        <v>106127</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2692,16 +2683,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2716,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715957</v>
+        <v>716099</v>
       </c>
       <c r="R20" t="n">
-        <v>6351748</v>
+        <v>6351734</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118787604</v>
+        <v>118787590</v>
       </c>
       <c r="B21" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,16 +2790,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2823,10 +2814,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>715937</v>
+        <v>715935</v>
       </c>
       <c r="R21" t="n">
-        <v>6351646</v>
+        <v>6351703</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2872,7 +2863,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2890,10 +2881,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118787681</v>
+        <v>118787755</v>
       </c>
       <c r="B22" t="n">
-        <v>106127</v>
+        <v>105502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2902,20 +2893,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2930,13 +2921,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716111</v>
+        <v>716067</v>
       </c>
       <c r="R22" t="n">
-        <v>6351576</v>
+        <v>6351944</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2966,6 +2957,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2997,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118787609</v>
+        <v>118787579</v>
       </c>
       <c r="B23" t="n">
-        <v>106127</v>
+        <v>98476</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3013,34 +3009,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221849</v>
+        <v>222295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715936</v>
+        <v>715987</v>
       </c>
       <c r="R23" t="n">
-        <v>6351658</v>
+        <v>6351753</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3075,6 +3080,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Backstarr kan inte helt uteslutas.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3086,7 +3096,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3104,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118787578</v>
+        <v>118787693</v>
       </c>
       <c r="B24" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3120,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3144,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716038</v>
+        <v>716098</v>
       </c>
       <c r="R24" t="n">
-        <v>6351750</v>
+        <v>6351710</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3211,10 +3221,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118787627</v>
+        <v>118787688</v>
       </c>
       <c r="B25" t="n">
-        <v>106783</v>
+        <v>106662</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3227,31 +3237,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>715996</v>
+        <v>716083</v>
       </c>
       <c r="R25" t="n">
         <v>6351660</v>
@@ -3287,6 +3306,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3318,10 +3342,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118787650</v>
+        <v>118787580</v>
       </c>
       <c r="B26" t="n">
-        <v>106662</v>
+        <v>103367</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3334,43 +3358,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1865</v>
+        <v>220164</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716014</v>
+        <v>715987</v>
       </c>
       <c r="R26" t="n">
-        <v>6351357</v>
+        <v>6351753</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3434,10 +3449,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118787755</v>
+        <v>118787587</v>
       </c>
       <c r="B27" t="n">
-        <v>105502</v>
+        <v>105743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,20 +3461,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>221903</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3474,13 +3489,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716067</v>
+        <v>715957</v>
       </c>
       <c r="R27" t="n">
-        <v>6351944</v>
+        <v>6351748</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3510,11 +3525,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3546,10 +3556,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118787735</v>
+        <v>118787756</v>
       </c>
       <c r="B28" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3562,16 +3572,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3586,13 +3596,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716068</v>
+        <v>716067</v>
       </c>
       <c r="R28" t="n">
-        <v>6351879</v>
+        <v>6351944</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3622,6 +3632,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3653,10 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118787733</v>
+        <v>118787653</v>
       </c>
       <c r="B29" t="n">
-        <v>105743</v>
+        <v>105502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3665,20 +3680,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221903</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3693,13 +3708,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716068</v>
+        <v>716128</v>
       </c>
       <c r="R29" t="n">
-        <v>6351879</v>
+        <v>6351284</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3742,7 +3757,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3760,10 +3775,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118787693</v>
+        <v>118787754</v>
       </c>
       <c r="B30" t="n">
-        <v>106783</v>
+        <v>105743</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3776,21 +3791,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3800,10 +3815,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716098</v>
+        <v>716069</v>
       </c>
       <c r="R30" t="n">
-        <v>6351710</v>
+        <v>6351918</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3867,10 +3882,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118787677</v>
+        <v>118787753</v>
       </c>
       <c r="B31" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3883,21 +3898,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3907,10 +3922,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716116</v>
+        <v>716069</v>
       </c>
       <c r="R31" t="n">
-        <v>6351568</v>
+        <v>6351918</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3974,10 +3989,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118787641</v>
+        <v>118787599</v>
       </c>
       <c r="B32" t="n">
-        <v>106783</v>
+        <v>105743</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3990,43 +4005,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220079</v>
+        <v>221903</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>715886</v>
+        <v>715881</v>
       </c>
       <c r="R32" t="n">
-        <v>6351326</v>
+        <v>6351621</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4072,7 +4078,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4090,10 +4096,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118787583</v>
+        <v>118787705</v>
       </c>
       <c r="B33" t="n">
-        <v>106783</v>
+        <v>106662</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4106,34 +4112,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715975</v>
+        <v>716089</v>
       </c>
       <c r="R33" t="n">
-        <v>6351761</v>
+        <v>6351790</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4179,7 +4194,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4309,10 +4324,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118787600</v>
+        <v>118787704</v>
       </c>
       <c r="B35" t="n">
-        <v>106127</v>
+        <v>103367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4325,21 +4340,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4349,10 +4364,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>715881</v>
+        <v>716089</v>
       </c>
       <c r="R35" t="n">
-        <v>6351621</v>
+        <v>6351790</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4398,7 +4413,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4416,10 +4431,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118787682</v>
+        <v>118787721</v>
       </c>
       <c r="B36" t="n">
-        <v>106127</v>
+        <v>106662</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4432,16 +4447,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4449,17 +4464,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>716105</v>
+        <v>716046</v>
       </c>
       <c r="R36" t="n">
-        <v>6351578</v>
+        <v>6351830</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4523,10 +4547,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118787585</v>
+        <v>118787673</v>
       </c>
       <c r="B37" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4539,21 +4563,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4563,10 +4587,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715975</v>
+        <v>716097</v>
       </c>
       <c r="R37" t="n">
-        <v>6351761</v>
+        <v>6351540</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4630,10 +4654,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118787713</v>
+        <v>118787608</v>
       </c>
       <c r="B38" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4646,16 +4670,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4670,10 +4694,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716068</v>
+        <v>715936</v>
       </c>
       <c r="R38" t="n">
-        <v>6351807</v>
+        <v>6351658</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4719,7 +4743,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4737,7 +4761,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118787581</v>
+        <v>118787588</v>
       </c>
       <c r="B39" t="n">
         <v>106127</v>
@@ -4777,10 +4801,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>715987</v>
+        <v>715957</v>
       </c>
       <c r="R39" t="n">
-        <v>6351753</v>
+        <v>6351748</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4844,10 +4868,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118787653</v>
+        <v>118787639</v>
       </c>
       <c r="B40" t="n">
-        <v>105502</v>
+        <v>106127</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4856,20 +4880,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4884,10 +4908,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716128</v>
+        <v>715847</v>
       </c>
       <c r="R40" t="n">
-        <v>6351284</v>
+        <v>6351378</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4933,7 +4957,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -4951,10 +4975,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118787698</v>
+        <v>118787727</v>
       </c>
       <c r="B41" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4967,16 +4991,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4984,26 +5008,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716099</v>
+        <v>716051</v>
       </c>
       <c r="R41" t="n">
-        <v>6351734</v>
+        <v>6351855</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5067,10 +5082,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118787721</v>
+        <v>118787600</v>
       </c>
       <c r="B42" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5083,16 +5098,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5100,26 +5115,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716046</v>
+        <v>715881</v>
       </c>
       <c r="R42" t="n">
-        <v>6351830</v>
+        <v>6351621</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5183,10 +5189,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118787666</v>
+        <v>118787596</v>
       </c>
       <c r="B43" t="n">
-        <v>106662</v>
+        <v>105743</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5199,16 +5205,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5216,26 +5222,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716106</v>
+        <v>715882</v>
       </c>
       <c r="R43" t="n">
-        <v>6351403</v>
+        <v>6351669</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5268,11 +5265,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5304,10 +5296,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118787772</v>
+        <v>118787720</v>
       </c>
       <c r="B44" t="n">
-        <v>42699</v>
+        <v>98476</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5320,41 +5312,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>101070</v>
+        <v>222295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5363,10 +5345,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>715921</v>
+        <v>716046</v>
       </c>
       <c r="R44" t="n">
-        <v>6351722</v>
+        <v>6351830</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5401,6 +5383,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5409,6 +5396,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5425,10 +5417,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118787592</v>
+        <v>118787637</v>
       </c>
       <c r="B45" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5441,21 +5433,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5465,13 +5457,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>715921</v>
+        <v>715847</v>
       </c>
       <c r="R45" t="n">
-        <v>6351722</v>
+        <v>6351378</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5514,7 +5506,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5532,10 +5524,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118787616</v>
+        <v>118787777</v>
       </c>
       <c r="B46" t="n">
-        <v>106127</v>
+        <v>42699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5548,37 +5540,56 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221849</v>
+        <v>101070</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>715954</v>
+        <v>716078</v>
       </c>
       <c r="R46" t="n">
-        <v>6351671</v>
+        <v>6351809</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5621,7 +5632,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -5639,10 +5650,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118787729</v>
+        <v>118787594</v>
       </c>
       <c r="B47" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5655,21 +5666,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5679,10 +5690,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716049</v>
+        <v>715906</v>
       </c>
       <c r="R47" t="n">
-        <v>6351866</v>
+        <v>6351711</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5746,10 +5757,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118787670</v>
+        <v>118787595</v>
       </c>
       <c r="B48" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5762,21 +5773,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5786,10 +5797,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716074</v>
+        <v>715904</v>
       </c>
       <c r="R48" t="n">
-        <v>6351539</v>
+        <v>6351691</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5853,10 +5864,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118787643</v>
+        <v>118787632</v>
       </c>
       <c r="B49" t="n">
-        <v>100114</v>
+        <v>106783</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5865,25 +5876,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5893,10 +5904,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>715897</v>
+        <v>716028</v>
       </c>
       <c r="R49" t="n">
-        <v>6351335</v>
+        <v>6351513</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5942,7 +5953,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5960,10 +5971,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118787718</v>
+        <v>118787643</v>
       </c>
       <c r="B50" t="n">
-        <v>105743</v>
+        <v>100114</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5972,25 +5983,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221903</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6000,10 +6011,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716046</v>
+        <v>715897</v>
       </c>
       <c r="R50" t="n">
-        <v>6351830</v>
+        <v>6351335</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6049,7 +6060,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6067,10 +6078,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118787622</v>
+        <v>118787583</v>
       </c>
       <c r="B51" t="n">
-        <v>105743</v>
+        <v>106783</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6083,21 +6094,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6107,10 +6118,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>715968</v>
+        <v>715975</v>
       </c>
       <c r="R51" t="n">
-        <v>6351681</v>
+        <v>6351761</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6156,7 +6167,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6174,10 +6185,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118787595</v>
+        <v>118787593</v>
       </c>
       <c r="B52" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6190,21 +6201,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6214,10 +6225,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>715904</v>
+        <v>715906</v>
       </c>
       <c r="R52" t="n">
-        <v>6351691</v>
+        <v>6351711</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6281,7 +6292,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118787700</v>
+        <v>118787630</v>
       </c>
       <c r="B53" t="n">
         <v>106127</v>
@@ -6321,10 +6332,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716089</v>
+        <v>716025</v>
       </c>
       <c r="R53" t="n">
-        <v>6351760</v>
+        <v>6351589</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6388,7 +6399,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118787584</v>
+        <v>118787718</v>
       </c>
       <c r="B54" t="n">
         <v>105743</v>
@@ -6428,10 +6439,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>715975</v>
+        <v>716046</v>
       </c>
       <c r="R54" t="n">
-        <v>6351761</v>
+        <v>6351830</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6495,10 +6506,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118787586</v>
+        <v>118787735</v>
       </c>
       <c r="B55" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6511,21 +6522,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6535,13 +6546,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>715957</v>
+        <v>716068</v>
       </c>
       <c r="R55" t="n">
-        <v>6351748</v>
+        <v>6351879</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6602,10 +6613,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118787593</v>
+        <v>118787725</v>
       </c>
       <c r="B56" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6618,21 +6629,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6642,10 +6653,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>715906</v>
+        <v>716048</v>
       </c>
       <c r="R56" t="n">
-        <v>6351711</v>
+        <v>6351840</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6709,10 +6720,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118787579</v>
+        <v>118787732</v>
       </c>
       <c r="B57" t="n">
-        <v>98476</v>
+        <v>106127</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6725,43 +6736,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222295</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>715987</v>
+        <v>716063</v>
       </c>
       <c r="R57" t="n">
-        <v>6351753</v>
+        <v>6351869</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6794,11 +6796,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6830,7 +6827,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118787671</v>
+        <v>118787694</v>
       </c>
       <c r="B58" t="n">
         <v>106127</v>
@@ -6870,10 +6867,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716074</v>
+        <v>716098</v>
       </c>
       <c r="R58" t="n">
-        <v>6351539</v>
+        <v>6351710</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6937,10 +6934,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118787577</v>
+        <v>118787586</v>
       </c>
       <c r="B59" t="n">
-        <v>106662</v>
+        <v>106783</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6953,46 +6950,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716038</v>
+        <v>715957</v>
       </c>
       <c r="R59" t="n">
-        <v>6351750</v>
+        <v>6351748</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7053,10 +7041,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118787680</v>
+        <v>118787628</v>
       </c>
       <c r="B60" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7069,21 +7057,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7093,10 +7081,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716111</v>
+        <v>715996</v>
       </c>
       <c r="R60" t="n">
-        <v>6351576</v>
+        <v>6351660</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7129,11 +7117,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7165,10 +7148,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118787669</v>
+        <v>118787667</v>
       </c>
       <c r="B61" t="n">
-        <v>106783</v>
+        <v>106662</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7181,34 +7164,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>716054</v>
+        <v>716086</v>
       </c>
       <c r="R61" t="n">
-        <v>6351534</v>
+        <v>6351456</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7272,10 +7264,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118787645</v>
+        <v>118787651</v>
       </c>
       <c r="B62" t="n">
-        <v>105502</v>
+        <v>106662</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7284,20 +7276,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220785</v>
+        <v>1865</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7305,17 +7297,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715913</v>
+        <v>716014</v>
       </c>
       <c r="R62" t="n">
-        <v>6351320</v>
+        <v>6351361</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7361,7 +7362,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7379,10 +7380,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118787753</v>
+        <v>118787685</v>
       </c>
       <c r="B63" t="n">
-        <v>106127</v>
+        <v>106662</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7395,16 +7396,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7412,17 +7413,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716069</v>
+        <v>716101</v>
       </c>
       <c r="R63" t="n">
-        <v>6351918</v>
+        <v>6351620</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7486,10 +7496,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118787684</v>
+        <v>118787676</v>
       </c>
       <c r="B64" t="n">
-        <v>103367</v>
+        <v>106662</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7502,37 +7512,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220164</v>
+        <v>1865</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>716101</v>
+        <v>716116</v>
       </c>
       <c r="R64" t="n">
-        <v>6351620</v>
+        <v>6351568</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7593,10 +7612,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118787725</v>
+        <v>118787645</v>
       </c>
       <c r="B65" t="n">
-        <v>106127</v>
+        <v>105502</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7605,20 +7624,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7633,10 +7652,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716048</v>
+        <v>715913</v>
       </c>
       <c r="R65" t="n">
-        <v>6351840</v>
+        <v>6351320</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7682,7 +7701,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7700,7 +7719,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787630</v>
+        <v>118787649</v>
       </c>
       <c r="B66" t="n">
         <v>106127</v>
@@ -7740,10 +7759,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716025</v>
+        <v>715990</v>
       </c>
       <c r="R66" t="n">
-        <v>6351589</v>
+        <v>6351309</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7807,10 +7826,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787726</v>
+        <v>118787723</v>
       </c>
       <c r="B67" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7823,21 +7842,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7847,10 +7866,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716051</v>
+        <v>716046</v>
       </c>
       <c r="R67" t="n">
-        <v>6351855</v>
+        <v>6351830</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7914,10 +7933,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787752</v>
+        <v>118787670</v>
       </c>
       <c r="B68" t="n">
-        <v>103367</v>
+        <v>106783</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7930,21 +7949,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7954,10 +7973,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>716069</v>
+        <v>716074</v>
       </c>
       <c r="R68" t="n">
-        <v>6351918</v>
+        <v>6351539</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8021,10 +8040,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787633</v>
+        <v>118787577</v>
       </c>
       <c r="B69" t="n">
-        <v>106127</v>
+        <v>106662</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8037,16 +8056,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8054,17 +8073,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716028</v>
+        <v>716038</v>
       </c>
       <c r="R69" t="n">
-        <v>6351513</v>
+        <v>6351750</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8128,10 +8156,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787703</v>
+        <v>118787686</v>
       </c>
       <c r="B70" t="n">
-        <v>99511</v>
+        <v>106783</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8144,43 +8172,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222617</v>
+        <v>220079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716089</v>
+        <v>716097</v>
       </c>
       <c r="R70" t="n">
-        <v>6351790</v>
+        <v>6351644</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8226,7 +8245,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8244,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787613</v>
+        <v>118787711</v>
       </c>
       <c r="B71" t="n">
-        <v>105743</v>
+        <v>106127</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8260,16 +8279,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8284,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>715954</v>
+        <v>716078</v>
       </c>
       <c r="R71" t="n">
-        <v>6351671</v>
+        <v>6351809</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8333,7 +8352,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8351,7 +8370,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118787732</v>
+        <v>118787604</v>
       </c>
       <c r="B72" t="n">
         <v>106127</v>
@@ -8391,10 +8410,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716063</v>
+        <v>715937</v>
       </c>
       <c r="R72" t="n">
-        <v>6351869</v>
+        <v>6351646</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8440,7 +8459,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8458,10 +8477,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118787676</v>
+        <v>118787616</v>
       </c>
       <c r="B73" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8474,16 +8493,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8491,29 +8510,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716116</v>
+        <v>715954</v>
       </c>
       <c r="R73" t="n">
-        <v>6351568</v>
+        <v>6351671</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8556,7 +8566,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8574,10 +8584,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118787731</v>
+        <v>118787772</v>
       </c>
       <c r="B74" t="n">
-        <v>106783</v>
+        <v>42699</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8590,34 +8600,53 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220079</v>
+        <v>101070</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716063</v>
+        <v>715921</v>
       </c>
       <c r="R74" t="n">
-        <v>6351869</v>
+        <v>6351722</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8660,11 +8689,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8681,10 +8705,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118787777</v>
+        <v>118787669</v>
       </c>
       <c r="B75" t="n">
-        <v>42699</v>
+        <v>106783</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8697,53 +8721,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>101070</v>
+        <v>220079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716078</v>
+        <v>716054</v>
       </c>
       <c r="R75" t="n">
-        <v>6351809</v>
+        <v>6351534</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8789,7 +8794,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8807,10 +8812,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118787754</v>
+        <v>118787734</v>
       </c>
       <c r="B76" t="n">
-        <v>105743</v>
+        <v>106783</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8823,21 +8828,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8847,10 +8852,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716069</v>
+        <v>716068</v>
       </c>
       <c r="R76" t="n">
-        <v>6351918</v>
+        <v>6351879</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8914,7 +8919,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118787599</v>
+        <v>118787712</v>
       </c>
       <c r="B77" t="n">
         <v>105743</v>
@@ -8954,10 +8959,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715881</v>
+        <v>716068</v>
       </c>
       <c r="R77" t="n">
-        <v>6351621</v>
+        <v>6351807</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9021,10 +9026,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118787649</v>
+        <v>118787733</v>
       </c>
       <c r="B78" t="n">
-        <v>106127</v>
+        <v>105743</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9037,16 +9042,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -9061,10 +9066,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>715990</v>
+        <v>716068</v>
       </c>
       <c r="R78" t="n">
-        <v>6351309</v>
+        <v>6351879</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9128,7 +9133,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118787727</v>
+        <v>118787681</v>
       </c>
       <c r="B79" t="n">
         <v>106127</v>
@@ -9168,10 +9173,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>716051</v>
+        <v>716111</v>
       </c>
       <c r="R79" t="n">
-        <v>6351855</v>
+        <v>6351576</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9235,10 +9240,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118787687</v>
+        <v>118787752</v>
       </c>
       <c r="B80" t="n">
-        <v>106662</v>
+        <v>103367</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9251,43 +9256,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1865</v>
+        <v>220164</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>716097</v>
+        <v>716069</v>
       </c>
       <c r="R80" t="n">
-        <v>6351644</v>
+        <v>6351918</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9322,11 +9318,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9338,7 +9329,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9356,7 +9347,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118787685</v>
+        <v>118787629</v>
       </c>
       <c r="B81" t="n">
         <v>106662</v>
@@ -9391,7 +9382,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -9405,10 +9396,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>716101</v>
+        <v>716025</v>
       </c>
       <c r="R81" t="n">
-        <v>6351620</v>
+        <v>6351589</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9441,6 +9432,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9472,10 +9468,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118787591</v>
+        <v>118787684</v>
       </c>
       <c r="B82" t="n">
-        <v>106127</v>
+        <v>103367</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9488,21 +9484,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9512,13 +9508,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>715935</v>
+        <v>716101</v>
       </c>
       <c r="R82" t="n">
-        <v>6351703</v>
+        <v>6351620</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9579,7 +9575,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118787734</v>
+        <v>118787726</v>
       </c>
       <c r="B83" t="n">
         <v>106783</v>
@@ -9619,10 +9615,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>716068</v>
+        <v>716051</v>
       </c>
       <c r="R83" t="n">
-        <v>6351879</v>
+        <v>6351855</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9686,10 +9682,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118787720</v>
+        <v>118787678</v>
       </c>
       <c r="B84" t="n">
-        <v>98476</v>
+        <v>106127</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9702,43 +9698,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222295</v>
+        <v>221849</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>716046</v>
+        <v>716116</v>
       </c>
       <c r="R84" t="n">
-        <v>6351830</v>
+        <v>6351568</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9771,11 +9758,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9807,10 +9789,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118787596</v>
+        <v>118787682</v>
       </c>
       <c r="B85" t="n">
-        <v>105743</v>
+        <v>106127</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9823,16 +9805,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9847,10 +9829,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715882</v>
+        <v>716105</v>
       </c>
       <c r="R85" t="n">
-        <v>6351669</v>
+        <v>6351578</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9914,10 +9896,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118787678</v>
+        <v>118787729</v>
       </c>
       <c r="B86" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9930,21 +9912,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9954,10 +9936,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>716116</v>
+        <v>716049</v>
       </c>
       <c r="R86" t="n">
-        <v>6351568</v>
+        <v>6351866</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10021,10 +10003,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118787730</v>
+        <v>118787751</v>
       </c>
       <c r="B87" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10037,21 +10019,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10061,10 +10043,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>716049</v>
+        <v>716069</v>
       </c>
       <c r="R87" t="n">
-        <v>6351866</v>
+        <v>6351918</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10128,10 +10110,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118787603</v>
+        <v>118787677</v>
       </c>
       <c r="B88" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10144,21 +10126,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10168,10 +10150,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715907</v>
+        <v>716116</v>
       </c>
       <c r="R88" t="n">
-        <v>6351637</v>
+        <v>6351568</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10217,7 +10199,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10235,10 +10217,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118787588</v>
+        <v>118787627</v>
       </c>
       <c r="B89" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10251,21 +10233,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10275,10 +10257,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715957</v>
+        <v>715996</v>
       </c>
       <c r="R89" t="n">
-        <v>6351748</v>
+        <v>6351660</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10342,10 +10324,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118787694</v>
+        <v>118787641</v>
       </c>
       <c r="B90" t="n">
-        <v>106127</v>
+        <v>106783</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10358,34 +10340,43 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>716098</v>
+        <v>715886</v>
       </c>
       <c r="R90" t="n">
-        <v>6351710</v>
+        <v>6351326</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10431,7 +10422,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10449,10 +10440,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118794857</v>
+        <v>118787622</v>
       </c>
       <c r="B91" t="n">
-        <v>57993</v>
+        <v>105743</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10465,33 +10456,24 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103055</v>
+        <v>221903</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
@@ -10501,10 +10483,10 @@
         <v>715968</v>
       </c>
       <c r="R91" t="n">
-        <v>6351687</v>
+        <v>6351681</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10547,7 +10529,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10565,10 +10547,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118787639</v>
+        <v>118787650</v>
       </c>
       <c r="B92" t="n">
-        <v>106127</v>
+        <v>106662</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10581,16 +10563,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -10598,20 +10580,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715847</v>
+        <v>716014</v>
       </c>
       <c r="R92" t="n">
-        <v>6351378</v>
+        <v>6351357</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10654,7 +10645,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10672,10 +10663,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118787632</v>
+        <v>118787687</v>
       </c>
       <c r="B93" t="n">
-        <v>106783</v>
+        <v>106662</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10688,34 +10679,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>716028</v>
+        <v>716097</v>
       </c>
       <c r="R93" t="n">
-        <v>6351513</v>
+        <v>6351644</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10750,6 +10750,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10761,7 +10766,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10779,10 +10784,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118787590</v>
+        <v>118787703</v>
       </c>
       <c r="B94" t="n">
-        <v>105743</v>
+        <v>99511</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10795,34 +10800,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221903</v>
+        <v>222617</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Phleum phleoides</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715935</v>
+        <v>716089</v>
       </c>
       <c r="R94" t="n">
-        <v>6351703</v>
+        <v>6351790</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10868,7 +10882,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10886,10 +10900,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118787667</v>
+        <v>118787592</v>
       </c>
       <c r="B95" t="n">
-        <v>106662</v>
+        <v>106127</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10902,16 +10916,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10919,26 +10933,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716086</v>
+        <v>715921</v>
       </c>
       <c r="R95" t="n">
-        <v>6351456</v>
+        <v>6351722</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11002,10 +11007,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118787724</v>
+        <v>118787603</v>
       </c>
       <c r="B96" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11018,21 +11023,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11042,10 +11047,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716048</v>
+        <v>715907</v>
       </c>
       <c r="R96" t="n">
-        <v>6351840</v>
+        <v>6351637</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11091,7 +11096,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11109,10 +11114,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118787637</v>
+        <v>118787617</v>
       </c>
       <c r="B97" t="n">
-        <v>106783</v>
+        <v>106127</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11125,21 +11130,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11149,13 +11154,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>715847</v>
+        <v>715968</v>
       </c>
       <c r="R97" t="n">
-        <v>6351378</v>
+        <v>6351681</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11198,7 +11203,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11216,10 +11221,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118787756</v>
+        <v>118787633</v>
       </c>
       <c r="B98" t="n">
-        <v>105743</v>
+        <v>106127</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11232,16 +11237,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11256,13 +11261,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716067</v>
+        <v>716028</v>
       </c>
       <c r="R98" t="n">
-        <v>6351944</v>
+        <v>6351513</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11292,11 +11297,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11328,7 +11328,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787594</v>
+        <v>118787671</v>
       </c>
       <c r="B99" t="n">
         <v>106127</v>
@@ -11368,10 +11368,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>715906</v>
+        <v>716074</v>
       </c>
       <c r="R99" t="n">
-        <v>6351711</v>
+        <v>6351539</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11435,7 +11435,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787617</v>
+        <v>118787591</v>
       </c>
       <c r="B100" t="n">
         <v>106127</v>
@@ -11475,10 +11475,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>715968</v>
+        <v>715935</v>
       </c>
       <c r="R100" t="n">
-        <v>6351681</v>
+        <v>6351703</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11524,7 +11524,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11542,7 +11542,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787651</v>
+        <v>118787652</v>
       </c>
       <c r="B101" t="n">
         <v>106662</v>
@@ -11591,10 +11591,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>716014</v>
+        <v>716032</v>
       </c>
       <c r="R101" t="n">
-        <v>6351361</v>
+        <v>6351369</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY101"/>
+  <dimension ref="A1:AY113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73371295</v>
+        <v>118787577</v>
       </c>
       <c r="B2" t="n">
-        <v>5410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105894</v>
+        <v>1865</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,29 +708,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Alvare, 500 m V, Gtl</t>
+          <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716164.6781527218</v>
+        <v>716038</v>
       </c>
       <c r="R2" t="n">
-        <v>6351218.857784627</v>
+        <v>6351750</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>talrika utgångshål i uppbrutna tallstubbar</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,33 +768,28 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>alvarmark med träd och buskar</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Ljungberg</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Ljungberg</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118787723</v>
+        <v>118787629</v>
       </c>
       <c r="B3" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -844,17 +814,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716046</v>
+        <v>716025</v>
       </c>
       <c r="R3" t="n">
-        <v>6351830</v>
+        <v>6351589</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118787754</v>
+        <v>118787650</v>
       </c>
       <c r="B4" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,17 +930,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716069</v>
+        <v>716014</v>
       </c>
       <c r="R4" t="n">
-        <v>6351918</v>
+        <v>6351357</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1025,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118787595</v>
+        <v>118787651</v>
       </c>
       <c r="B5" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,16 +1024,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1058,17 +1041,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>715904</v>
+        <v>716014</v>
       </c>
       <c r="R5" t="n">
-        <v>6351691</v>
+        <v>6351361</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1132,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118787673</v>
+        <v>118787652</v>
       </c>
       <c r="B6" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,34 +1135,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716097</v>
+        <v>716032</v>
       </c>
       <c r="R6" t="n">
-        <v>6351540</v>
+        <v>6351369</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1239,15 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118787677</v>
+        <v>118787666</v>
       </c>
       <c r="B7" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,34 +1246,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716116</v>
+        <v>716106</v>
       </c>
       <c r="R7" t="n">
-        <v>6351568</v>
+        <v>6351403</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,6 +1315,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,15 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118787593</v>
+        <v>118787667</v>
       </c>
       <c r="B8" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,34 +1362,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>715906</v>
+        <v>716086</v>
       </c>
       <c r="R8" t="n">
-        <v>6351711</v>
+        <v>6351456</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1453,15 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118787632</v>
+        <v>118787676</v>
       </c>
       <c r="B9" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,34 +1473,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716028</v>
+        <v>716116</v>
       </c>
       <c r="R9" t="n">
-        <v>6351513</v>
+        <v>6351568</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1560,15 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118787777</v>
+        <v>118787685</v>
       </c>
       <c r="B10" t="n">
-        <v>42699</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,21 +1584,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101070</v>
+        <v>1865</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1600,17 +1608,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1619,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716078</v>
+        <v>716101</v>
       </c>
       <c r="R10" t="n">
-        <v>6351809</v>
+        <v>6351620</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1668,7 +1666,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1686,15 +1684,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118787669</v>
+        <v>118787687</v>
       </c>
       <c r="B11" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,34 +1695,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220079</v>
+        <v>1865</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716054</v>
+        <v>716097</v>
       </c>
       <c r="R11" t="n">
-        <v>6351534</v>
+        <v>6351644</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1764,6 +1766,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1775,7 +1782,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1793,15 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118787700</v>
+        <v>118787688</v>
       </c>
       <c r="B12" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,16 +1811,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1826,17 +1828,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716089</v>
+        <v>716083</v>
       </c>
       <c r="R12" t="n">
-        <v>6351760</v>
+        <v>6351660</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1869,6 +1880,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,15 +1916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118787639</v>
+        <v>118787698</v>
       </c>
       <c r="B13" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,16 +1927,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1933,20 +1944,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>715847</v>
+        <v>716099</v>
       </c>
       <c r="R13" t="n">
-        <v>6351378</v>
+        <v>6351734</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,7 +2009,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2007,15 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118787587</v>
+        <v>118787705</v>
       </c>
       <c r="B14" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2023,16 +2038,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>1865</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2040,17 +2055,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>715957</v>
+        <v>716089</v>
       </c>
       <c r="R14" t="n">
-        <v>6351748</v>
+        <v>6351790</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2096,7 +2120,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2114,15 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118787603</v>
+        <v>118787706</v>
       </c>
       <c r="B15" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2130,16 +2149,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2147,17 +2166,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>715907</v>
+        <v>716091</v>
       </c>
       <c r="R15" t="n">
-        <v>6351637</v>
+        <v>6351798</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2203,7 +2231,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2221,15 +2249,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118787628</v>
+        <v>118787721</v>
       </c>
       <c r="B16" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,16 +2260,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2254,17 +2277,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>715996</v>
+        <v>716046</v>
       </c>
       <c r="R16" t="n">
-        <v>6351660</v>
+        <v>6351830</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2328,15 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118787609</v>
+        <v>118787737</v>
       </c>
       <c r="B17" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2344,16 +2371,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221849</v>
+        <v>1865</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2361,20 +2388,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>När Alvare 1:6 (2), Gtl</t>
+          <t>När Alvare 1:2 (1), Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>715936</v>
+        <v>716096</v>
       </c>
       <c r="R17" t="n">
-        <v>6351658</v>
+        <v>6351873</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2406,6 +2442,11 @@
           <t>2024-07-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2417,7 +2458,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2435,15 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118794857</v>
+        <v>118787748</v>
       </c>
       <c r="B18" t="n">
-        <v>57995</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107995</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,31 +2487,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103055</v>
+        <v>1865</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Piggtistel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Carduus acanthoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2484,13 +2520,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>715968</v>
+        <v>716076</v>
       </c>
       <c r="R18" t="n">
-        <v>6351687</v>
+        <v>6351902</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,15 +2587,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118787726</v>
+        <v>118787772</v>
       </c>
       <c r="B19" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2567,34 +2598,53 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220079</v>
+        <v>101070</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716051</v>
+        <v>715921</v>
       </c>
       <c r="R19" t="n">
-        <v>6351855</v>
+        <v>6351722</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2637,11 +2687,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2658,15 +2703,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118787617</v>
+        <v>118787777</v>
       </c>
       <c r="B20" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43212</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,34 +2714,53 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221849</v>
+        <v>101070</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>715968</v>
+        <v>716078</v>
       </c>
       <c r="R20" t="n">
-        <v>6351681</v>
+        <v>6351809</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2747,7 +2806,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat. På backtimjan.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2765,15 +2824,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118787652</v>
+        <v>118794857</v>
       </c>
       <c r="B21" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2781,31 +2835,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1865</v>
+        <v>103055</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2814,13 +2868,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716032</v>
+        <v>715968</v>
       </c>
       <c r="R21" t="n">
-        <v>6351369</v>
+        <v>6351687</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2881,15 +2935,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118787711</v>
+        <v>73371295</v>
       </c>
       <c r="B22" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5479</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2897,37 +2946,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221849</v>
+        <v>105894</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1761)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>När Alvare 1:6 (2), Gtl</t>
+          <t>Alvare, 500 m V, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716078</v>
+        <v>716165</v>
       </c>
       <c r="R22" t="n">
-        <v>6351809</v>
+        <v>6351219</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2951,12 +3014,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2018-08-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2018-08-25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>talrika utgångshål i uppbrutna tallstubbar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2970,33 +3038,28 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>alvarmark med träd och buskar</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Håkan Ljungberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Håkan Ljungberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118787622</v>
+        <v>118787583</v>
       </c>
       <c r="B23" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,21 +3067,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3091,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>715968</v>
+        <v>715975</v>
       </c>
       <c r="R23" t="n">
-        <v>6351681</v>
+        <v>6351761</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3077,7 +3140,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3095,15 +3158,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118787682</v>
+        <v>118787586</v>
       </c>
       <c r="B24" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3169,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716105</v>
+        <v>715957</v>
       </c>
       <c r="R24" t="n">
-        <v>6351578</v>
+        <v>6351748</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3202,15 +3260,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118787671</v>
+        <v>118787593</v>
       </c>
       <c r="B25" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,21 +3271,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716074</v>
+        <v>715906</v>
       </c>
       <c r="R25" t="n">
-        <v>6351539</v>
+        <v>6351711</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3309,15 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118787581</v>
+        <v>118787627</v>
       </c>
       <c r="B26" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,21 +3373,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3349,10 +3397,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>715987</v>
+        <v>715996</v>
       </c>
       <c r="R26" t="n">
-        <v>6351753</v>
+        <v>6351660</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3416,37 +3464,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118787653</v>
+        <v>118787632</v>
       </c>
       <c r="B27" t="n">
-        <v>105507</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3456,13 +3499,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716128</v>
+        <v>716028</v>
       </c>
       <c r="R27" t="n">
-        <v>6351284</v>
+        <v>6351513</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3505,7 +3548,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3523,15 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118787608</v>
+        <v>118787637</v>
       </c>
       <c r="B28" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3539,21 +3577,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3563,13 +3601,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>715936</v>
+        <v>715847</v>
       </c>
       <c r="R28" t="n">
-        <v>6351658</v>
+        <v>6351378</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3612,7 +3650,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3630,15 +3668,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118787594</v>
+        <v>118787641</v>
       </c>
       <c r="B29" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3646,34 +3679,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>715906</v>
+        <v>715886</v>
       </c>
       <c r="R29" t="n">
-        <v>6351711</v>
+        <v>6351326</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3719,7 +3761,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3737,15 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118787599</v>
+        <v>118787642</v>
       </c>
       <c r="B30" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3753,21 +3790,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3777,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>715881</v>
+        <v>715897</v>
       </c>
       <c r="R30" t="n">
-        <v>6351621</v>
+        <v>6351335</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3826,7 +3863,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3844,37 +3881,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118787643</v>
+        <v>118787669</v>
       </c>
       <c r="B31" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3884,10 +3916,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>715897</v>
+        <v>716054</v>
       </c>
       <c r="R31" t="n">
-        <v>6351335</v>
+        <v>6351534</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3933,7 +3965,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3951,15 +3983,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118787684</v>
+        <v>118787670</v>
       </c>
       <c r="B32" t="n">
-        <v>103372</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,21 +3994,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220164</v>
+        <v>220079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3991,13 +4018,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716101</v>
+        <v>716074</v>
       </c>
       <c r="R32" t="n">
-        <v>6351620</v>
+        <v>6351539</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4058,15 +4085,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118787613</v>
+        <v>118787673</v>
       </c>
       <c r="B33" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4074,21 +4096,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4098,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>715954</v>
+        <v>716097</v>
       </c>
       <c r="R33" t="n">
-        <v>6351671</v>
+        <v>6351540</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4147,7 +4169,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4165,15 +4187,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118787591</v>
+        <v>118787677</v>
       </c>
       <c r="B34" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4181,21 +4198,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4205,10 +4222,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>715935</v>
+        <v>716116</v>
       </c>
       <c r="R34" t="n">
-        <v>6351703</v>
+        <v>6351568</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4272,15 +4289,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118787698</v>
+        <v>118787680</v>
       </c>
       <c r="B35" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4288,43 +4300,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>716099</v>
+        <v>716111</v>
       </c>
       <c r="R35" t="n">
-        <v>6351734</v>
+        <v>6351576</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4357,6 +4360,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4388,15 +4396,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118787630</v>
+        <v>118787686</v>
       </c>
       <c r="B36" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4404,21 +4407,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4428,10 +4431,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>716025</v>
+        <v>716097</v>
       </c>
       <c r="R36" t="n">
-        <v>6351589</v>
+        <v>6351644</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4495,15 +4498,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118787616</v>
+        <v>118787693</v>
       </c>
       <c r="B37" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4511,21 +4509,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4535,13 +4533,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>715954</v>
+        <v>716098</v>
       </c>
       <c r="R37" t="n">
-        <v>6351671</v>
+        <v>6351710</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4584,7 +4582,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4602,15 +4600,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118787588</v>
+        <v>118787710</v>
       </c>
       <c r="B38" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4618,21 +4611,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4642,10 +4635,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>715957</v>
+        <v>716091</v>
       </c>
       <c r="R38" t="n">
-        <v>6351748</v>
+        <v>6351809</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4709,15 +4702,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118787732</v>
+        <v>118787722</v>
       </c>
       <c r="B39" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4725,21 +4713,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4749,10 +4737,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>716063</v>
+        <v>716046</v>
       </c>
       <c r="R39" t="n">
-        <v>6351869</v>
+        <v>6351830</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4816,15 +4804,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118787734</v>
+        <v>118787724</v>
       </c>
       <c r="B40" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4856,10 +4839,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716068</v>
+        <v>716048</v>
       </c>
       <c r="R40" t="n">
-        <v>6351879</v>
+        <v>6351840</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4923,15 +4906,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118787686</v>
+        <v>118787726</v>
       </c>
       <c r="B41" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4963,10 +4941,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716097</v>
+        <v>716051</v>
       </c>
       <c r="R41" t="n">
-        <v>6351644</v>
+        <v>6351855</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5030,15 +5008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118787718</v>
+        <v>118787729</v>
       </c>
       <c r="B42" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5046,21 +5019,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5070,10 +5043,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716046</v>
+        <v>716049</v>
       </c>
       <c r="R42" t="n">
-        <v>6351830</v>
+        <v>6351866</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5137,15 +5110,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118787590</v>
+        <v>118787731</v>
       </c>
       <c r="B43" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5153,21 +5121,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221903</v>
+        <v>220079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5177,10 +5145,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>715935</v>
+        <v>716063</v>
       </c>
       <c r="R43" t="n">
-        <v>6351703</v>
+        <v>6351869</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5244,15 +5212,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118787720</v>
+        <v>118787734</v>
       </c>
       <c r="B44" t="n">
-        <v>98481</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5260,43 +5223,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222295</v>
+        <v>220079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716046</v>
+        <v>716068</v>
       </c>
       <c r="R44" t="n">
-        <v>6351830</v>
+        <v>6351879</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5329,11 +5283,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5365,15 +5314,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118787685</v>
+        <v>118787747</v>
       </c>
       <c r="B45" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5381,43 +5325,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1865</v>
+        <v>220079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716101</v>
+        <v>716076</v>
       </c>
       <c r="R45" t="n">
-        <v>6351620</v>
+        <v>6351902</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5481,15 +5416,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118787731</v>
+        <v>118787751</v>
       </c>
       <c r="B46" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5521,10 +5451,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716063</v>
+        <v>716069</v>
       </c>
       <c r="R46" t="n">
-        <v>6351869</v>
+        <v>6351918</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5588,15 +5518,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118787633</v>
+        <v>118787580</v>
       </c>
       <c r="B47" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5604,21 +5529,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5628,10 +5553,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>716028</v>
+        <v>715987</v>
       </c>
       <c r="R47" t="n">
-        <v>6351513</v>
+        <v>6351753</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5695,15 +5620,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118787695</v>
+        <v>118787684</v>
       </c>
       <c r="B48" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5711,21 +5631,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5735,10 +5655,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716099</v>
+        <v>716101</v>
       </c>
       <c r="R48" t="n">
-        <v>6351734</v>
+        <v>6351620</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5802,15 +5722,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118787694</v>
+        <v>118787704</v>
       </c>
       <c r="B49" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5818,21 +5733,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221849</v>
+        <v>220164</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5842,10 +5757,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716098</v>
+        <v>716089</v>
       </c>
       <c r="R49" t="n">
-        <v>6351710</v>
+        <v>6351790</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5891,7 +5806,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5909,15 +5824,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118787680</v>
+        <v>118787707</v>
       </c>
       <c r="B50" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5925,21 +5835,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220079</v>
+        <v>220164</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5949,10 +5859,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716111</v>
+        <v>716091</v>
       </c>
       <c r="R50" t="n">
-        <v>6351576</v>
+        <v>6351798</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5985,11 +5895,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6021,15 +5926,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118787705</v>
+        <v>118787752</v>
       </c>
       <c r="B51" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6037,43 +5937,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1865</v>
+        <v>220164</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>716089</v>
+        <v>716069</v>
       </c>
       <c r="R51" t="n">
-        <v>6351790</v>
+        <v>6351918</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6119,7 +6010,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6137,37 +6028,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118787724</v>
+        <v>118787645</v>
       </c>
       <c r="B52" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6177,10 +6063,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>716048</v>
+        <v>715913</v>
       </c>
       <c r="R52" t="n">
-        <v>6351840</v>
+        <v>6351320</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6226,7 +6112,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6244,15 +6130,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118787755</v>
+        <v>118787653</v>
       </c>
       <c r="B53" t="n">
-        <v>105507</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6284,10 +6165,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716067</v>
+        <v>716128</v>
       </c>
       <c r="R53" t="n">
-        <v>6351944</v>
+        <v>6351284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6322,11 +6203,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6338,7 +6214,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Fuktsvacka nära upplag.</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6356,32 +6232,27 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118787735</v>
+        <v>118787755</v>
       </c>
       <c r="B54" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6396,13 +6267,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716068</v>
+        <v>716067</v>
       </c>
       <c r="R54" t="n">
-        <v>6351879</v>
+        <v>6351944</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6432,6 +6303,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6463,15 +6339,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118787681</v>
+        <v>118787576</v>
       </c>
       <c r="B55" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6503,10 +6374,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716111</v>
+        <v>716038</v>
       </c>
       <c r="R55" t="n">
-        <v>6351576</v>
+        <v>6351750</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6570,15 +6441,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118787753</v>
+        <v>118787581</v>
       </c>
       <c r="B56" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6610,10 +6476,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716069</v>
+        <v>715987</v>
       </c>
       <c r="R56" t="n">
-        <v>6351918</v>
+        <v>6351753</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6677,15 +6543,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118787650</v>
+        <v>118787585</v>
       </c>
       <c r="B57" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6693,16 +6554,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6710,26 +6571,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716014</v>
+        <v>715975</v>
       </c>
       <c r="R57" t="n">
-        <v>6351357</v>
+        <v>6351761</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6793,15 +6645,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118787713</v>
+        <v>118787588</v>
       </c>
       <c r="B58" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6833,10 +6680,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716068</v>
+        <v>715957</v>
       </c>
       <c r="R58" t="n">
-        <v>6351807</v>
+        <v>6351748</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6900,15 +6747,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118787712</v>
+        <v>118787591</v>
       </c>
       <c r="B59" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6916,16 +6758,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6940,10 +6782,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716068</v>
+        <v>715935</v>
       </c>
       <c r="R59" t="n">
-        <v>6351807</v>
+        <v>6351703</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7007,15 +6849,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118787722</v>
+        <v>118787592</v>
       </c>
       <c r="B60" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7023,21 +6860,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7047,10 +6884,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716046</v>
+        <v>715921</v>
       </c>
       <c r="R60" t="n">
-        <v>6351830</v>
+        <v>6351722</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7114,15 +6951,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118787670</v>
+        <v>118787594</v>
       </c>
       <c r="B61" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7130,21 +6962,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7154,10 +6986,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>716074</v>
+        <v>715906</v>
       </c>
       <c r="R61" t="n">
-        <v>6351539</v>
+        <v>6351711</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7221,15 +7053,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118787641</v>
+        <v>118787595</v>
       </c>
       <c r="B62" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7237,43 +7064,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>715886</v>
+        <v>715904</v>
       </c>
       <c r="R62" t="n">
-        <v>6351326</v>
+        <v>6351691</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7319,7 +7137,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7337,15 +7155,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118787604</v>
+        <v>118787600</v>
       </c>
       <c r="B63" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7377,10 +7190,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>715937</v>
+        <v>715881</v>
       </c>
       <c r="R63" t="n">
-        <v>6351646</v>
+        <v>6351621</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7426,7 +7239,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7444,15 +7257,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118787585</v>
+        <v>118787603</v>
       </c>
       <c r="B64" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7484,10 +7292,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>715975</v>
+        <v>715907</v>
       </c>
       <c r="R64" t="n">
-        <v>6351761</v>
+        <v>6351637</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7533,7 +7341,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Silkatstensområde (grav?).</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7551,15 +7359,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118787676</v>
+        <v>118787604</v>
       </c>
       <c r="B65" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7567,16 +7370,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -7584,26 +7387,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716116</v>
+        <v>715937</v>
       </c>
       <c r="R65" t="n">
-        <v>6351568</v>
+        <v>6351646</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7649,7 +7443,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7667,15 +7461,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118787725</v>
+        <v>118787609</v>
       </c>
       <c r="B66" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7707,10 +7496,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716048</v>
+        <v>715936</v>
       </c>
       <c r="R66" t="n">
-        <v>6351840</v>
+        <v>6351658</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7756,7 +7545,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7774,15 +7563,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118787704</v>
+        <v>118787616</v>
       </c>
       <c r="B67" t="n">
-        <v>103372</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7790,21 +7574,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7814,13 +7598,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716089</v>
+        <v>715954</v>
       </c>
       <c r="R67" t="n">
-        <v>6351790</v>
+        <v>6351671</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7863,7 +7647,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7881,15 +7665,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118787637</v>
+        <v>118787617</v>
       </c>
       <c r="B68" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7897,21 +7676,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7921,13 +7700,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>715847</v>
+        <v>715968</v>
       </c>
       <c r="R68" t="n">
-        <v>6351378</v>
+        <v>6351681</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7970,7 +7749,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7988,15 +7767,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118787649</v>
+        <v>118787628</v>
       </c>
       <c r="B69" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8028,10 +7802,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>715990</v>
+        <v>715996</v>
       </c>
       <c r="R69" t="n">
-        <v>6351309</v>
+        <v>6351660</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8095,15 +7869,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118787730</v>
+        <v>118787630</v>
       </c>
       <c r="B70" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8135,10 +7904,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716049</v>
+        <v>716025</v>
       </c>
       <c r="R70" t="n">
-        <v>6351866</v>
+        <v>6351589</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8202,15 +7971,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118787578</v>
+        <v>118787633</v>
       </c>
       <c r="B71" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8242,10 +8006,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>716038</v>
+        <v>716028</v>
       </c>
       <c r="R71" t="n">
-        <v>6351750</v>
+        <v>6351513</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8309,15 +8073,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118787584</v>
+        <v>118787639</v>
       </c>
       <c r="B72" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8325,16 +8084,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8349,13 +8108,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>715975</v>
+        <v>715847</v>
       </c>
       <c r="R72" t="n">
-        <v>6351761</v>
+        <v>6351378</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8398,7 +8157,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8416,15 +8175,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118787666</v>
+        <v>118787649</v>
       </c>
       <c r="B73" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8432,16 +8186,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8449,26 +8203,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716106</v>
+        <v>715990</v>
       </c>
       <c r="R73" t="n">
-        <v>6351403</v>
+        <v>6351309</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8501,11 +8246,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Inom 15 m.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8537,15 +8277,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118787729</v>
+        <v>118787668</v>
       </c>
       <c r="B74" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8553,21 +8288,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8577,10 +8312,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716049</v>
+        <v>716076</v>
       </c>
       <c r="R74" t="n">
-        <v>6351866</v>
+        <v>6351474</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8613,6 +8348,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8644,15 +8384,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118787592</v>
+        <v>118787671</v>
       </c>
       <c r="B75" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8684,10 +8419,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>715921</v>
+        <v>716074</v>
       </c>
       <c r="R75" t="n">
-        <v>6351722</v>
+        <v>6351539</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8751,15 +8486,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118787727</v>
+        <v>118787678</v>
       </c>
       <c r="B76" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8791,10 +8521,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716051</v>
+        <v>716116</v>
       </c>
       <c r="R76" t="n">
-        <v>6351855</v>
+        <v>6351568</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8858,15 +8588,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118787596</v>
+        <v>118787681</v>
       </c>
       <c r="B77" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8874,16 +8599,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221903</v>
+        <v>221849</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8898,10 +8623,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>715882</v>
+        <v>716111</v>
       </c>
       <c r="R77" t="n">
-        <v>6351669</v>
+        <v>6351576</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8965,15 +8690,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118787703</v>
+        <v>118787682</v>
       </c>
       <c r="B78" t="n">
-        <v>99516</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8981,43 +8701,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222617</v>
+        <v>221849</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716089</v>
+        <v>716105</v>
       </c>
       <c r="R78" t="n">
-        <v>6351790</v>
+        <v>6351578</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9063,7 +8774,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9081,15 +8792,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118787688</v>
+        <v>118787694</v>
       </c>
       <c r="B79" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9097,16 +8803,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9114,26 +8820,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>716083</v>
+        <v>716098</v>
       </c>
       <c r="R79" t="n">
-        <v>6351660</v>
+        <v>6351710</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9166,11 +8863,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9202,15 +8894,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118787651</v>
+        <v>118787695</v>
       </c>
       <c r="B80" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9218,16 +8905,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9235,29 +8922,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>716014</v>
+        <v>716099</v>
       </c>
       <c r="R80" t="n">
-        <v>6351361</v>
+        <v>6351734</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9318,15 +8996,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118787600</v>
+        <v>118787700</v>
       </c>
       <c r="B81" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9358,10 +9031,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>715881</v>
+        <v>716089</v>
       </c>
       <c r="R81" t="n">
-        <v>6351621</v>
+        <v>6351760</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9425,15 +9098,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118787577</v>
+        <v>118787711</v>
       </c>
       <c r="B82" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9441,16 +9109,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1865</v>
+        <v>221849</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9458,26 +9126,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716038</v>
+        <v>716078</v>
       </c>
       <c r="R82" t="n">
-        <v>6351750</v>
+        <v>6351809</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9541,15 +9200,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118787693</v>
+        <v>118787713</v>
       </c>
       <c r="B83" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9557,21 +9211,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9581,10 +9235,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>716098</v>
+        <v>716068</v>
       </c>
       <c r="R83" t="n">
-        <v>6351710</v>
+        <v>6351807</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9648,15 +9302,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118787627</v>
+        <v>118787719</v>
       </c>
       <c r="B84" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9664,21 +9313,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9688,10 +9337,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>715996</v>
+        <v>716046</v>
       </c>
       <c r="R84" t="n">
-        <v>6351660</v>
+        <v>6351830</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9755,32 +9404,27 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118787645</v>
+        <v>118787725</v>
       </c>
       <c r="B85" t="n">
-        <v>105507</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220785</v>
+        <v>221849</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9795,10 +9439,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>715913</v>
+        <v>716048</v>
       </c>
       <c r="R85" t="n">
-        <v>6351320</v>
+        <v>6351840</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9844,7 +9488,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9862,15 +9506,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118787668</v>
+        <v>118787727</v>
       </c>
       <c r="B86" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9902,10 +9541,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>716076</v>
+        <v>716051</v>
       </c>
       <c r="R86" t="n">
-        <v>6351474</v>
+        <v>6351855</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9938,11 +9577,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9974,15 +9608,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118787772</v>
+        <v>118787730</v>
       </c>
       <c r="B87" t="n">
-        <v>42699</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9990,53 +9619,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>101070</v>
+        <v>221849</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>715921</v>
+        <v>716049</v>
       </c>
       <c r="R87" t="n">
-        <v>6351722</v>
+        <v>6351866</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10079,6 +9689,11 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10095,15 +9710,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118787586</v>
+        <v>118787732</v>
       </c>
       <c r="B88" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10111,21 +9721,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10135,13 +9745,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>715957</v>
+        <v>716063</v>
       </c>
       <c r="R88" t="n">
-        <v>6351748</v>
+        <v>6351869</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10202,15 +9812,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118787583</v>
+        <v>118787735</v>
       </c>
       <c r="B89" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10218,21 +9823,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10242,10 +9847,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>715975</v>
+        <v>716068</v>
       </c>
       <c r="R89" t="n">
-        <v>6351761</v>
+        <v>6351879</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10309,15 +9914,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118787751</v>
+        <v>118787736</v>
       </c>
       <c r="B90" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10325,21 +9925,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10349,10 +9949,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>716069</v>
+        <v>716079</v>
       </c>
       <c r="R90" t="n">
-        <v>6351918</v>
+        <v>6351880</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10416,15 +10016,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118787642</v>
+        <v>118787749</v>
       </c>
       <c r="B91" t="n">
-        <v>106788</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10432,21 +10027,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10456,10 +10051,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>715897</v>
+        <v>716076</v>
       </c>
       <c r="R91" t="n">
-        <v>6351335</v>
+        <v>6351902</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10505,7 +10100,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10523,15 +10118,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118787580</v>
+        <v>118787753</v>
       </c>
       <c r="B92" t="n">
-        <v>103372</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10539,21 +10129,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220164</v>
+        <v>221849</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10563,10 +10153,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>715987</v>
+        <v>716069</v>
       </c>
       <c r="R92" t="n">
-        <v>6351753</v>
+        <v>6351918</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10630,15 +10220,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118787678</v>
+        <v>118787584</v>
       </c>
       <c r="B93" t="n">
-        <v>106132</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10646,16 +10231,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221849</v>
+        <v>221903</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -10670,10 +10255,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>716116</v>
+        <v>715975</v>
       </c>
       <c r="R93" t="n">
-        <v>6351568</v>
+        <v>6351761</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10737,15 +10322,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118787579</v>
+        <v>118787587</v>
       </c>
       <c r="B94" t="n">
-        <v>98481</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10753,43 +10333,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222295</v>
+        <v>221903</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>715987</v>
+        <v>715957</v>
       </c>
       <c r="R94" t="n">
-        <v>6351753</v>
+        <v>6351748</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10822,11 +10393,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Backstarr kan inte helt uteslutas.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10858,15 +10424,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118787667</v>
+        <v>118787590</v>
       </c>
       <c r="B95" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10874,16 +10435,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -10891,26 +10452,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716086</v>
+        <v>715935</v>
       </c>
       <c r="R95" t="n">
-        <v>6351456</v>
+        <v>6351703</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10974,15 +10526,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118787752</v>
+        <v>118787596</v>
       </c>
       <c r="B96" t="n">
-        <v>103372</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10990,21 +10537,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220164</v>
+        <v>221903</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11014,10 +10561,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716069</v>
+        <v>715882</v>
       </c>
       <c r="R96" t="n">
-        <v>6351918</v>
+        <v>6351669</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11081,15 +10628,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118787756</v>
+        <v>118787599</v>
       </c>
       <c r="B97" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11121,13 +10663,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716067</v>
+        <v>715881</v>
       </c>
       <c r="R97" t="n">
-        <v>6351944</v>
+        <v>6351621</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11157,11 +10699,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Svårframkomligt; slån, en.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11193,15 +10730,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118787687</v>
+        <v>118787608</v>
       </c>
       <c r="B98" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11209,16 +10741,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -11226,26 +10758,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716097</v>
+        <v>715936</v>
       </c>
       <c r="R98" t="n">
-        <v>6351644</v>
+        <v>6351658</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11280,11 +10803,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Inom 20 m.</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11296,7 +10814,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat. På stenrad (stensträng, stenmur?).</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11314,15 +10832,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118787721</v>
+        <v>118787613</v>
       </c>
       <c r="B99" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11330,16 +10843,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -11347,26 +10860,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716046</v>
+        <v>715954</v>
       </c>
       <c r="R99" t="n">
-        <v>6351830</v>
+        <v>6351671</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11412,7 +10916,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11430,15 +10934,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118787733</v>
+        <v>118787622</v>
       </c>
       <c r="B100" t="n">
-        <v>105748</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11470,10 +10969,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>716068</v>
+        <v>715968</v>
       </c>
       <c r="R100" t="n">
-        <v>6351879</v>
+        <v>6351681</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11519,7 +11018,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>Alvarmark, igenväxande; nötbetat.</t>
+          <t>Alvarmark, igenväxande; nötbetat. Förmodligen något vinterfuktigt.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11537,15 +11036,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118787629</v>
+        <v>118787708</v>
       </c>
       <c r="B101" t="n">
-        <v>106667</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107061</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11553,16 +11047,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1865</v>
+        <v>221903</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Piggtistel</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carduus acanthoides</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -11570,26 +11064,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>När Alvare 1:6 (2), Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>716025</v>
+        <v>716091</v>
       </c>
       <c r="R101" t="n">
-        <v>6351589</v>
+        <v>6351798</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11624,11 +11109,6 @@
           <t>2024-07-26</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Spridd längs stensträng mot V och O samt norrut ca 30 m mot och vid röse. Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -11655,6 +11135,1295 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>118787712</v>
+      </c>
+      <c r="B102" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>716068</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6351807</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>118787718</v>
+      </c>
+      <c r="B103" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>716046</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6351830</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>118787733</v>
+      </c>
+      <c r="B104" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>716068</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6351879</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>118787750</v>
+      </c>
+      <c r="B105" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>716076</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6351902</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>118787754</v>
+      </c>
+      <c r="B106" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>716069</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6351918</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>118787756</v>
+      </c>
+      <c r="B107" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>716067</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6351944</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Svårframkomligt; slån, en.</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>118787579</v>
+      </c>
+      <c r="B108" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>715987</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6351753</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Backstarr kan inte helt uteslutas.</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>118787720</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>716046</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6351830</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>118787743</v>
+      </c>
+      <c r="B110" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>716076</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6351902</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Minsta antal; backstarr kan inte fullt ut uteslutas.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>118787643</v>
+      </c>
+      <c r="B111" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>715897</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6351335</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>Tallskog, utvecklöad på lermärgel; troligen igenvuxen f.d. alvarmark. Mycket tynne. Nöttrampade stigar.</t>
+        </is>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>118787703</v>
+      </c>
+      <c r="B112" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>716089</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6351790</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat. Gravfält.</t>
+        </is>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>118787709</v>
+      </c>
+      <c r="B113" t="n">
+        <v>100798</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222617</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Flentimotej</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>När Alvare 1:6 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>716091</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6351798</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>När</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>Alvarmark, igenväxande; nötbetat.</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28287-2024 artfynd.xlsx
+++ b/artfynd/A 28287-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787577</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787629</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787650</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787651</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787652</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787666</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787667</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787676</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1681,6 +1726,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787685</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787687</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,6 +1968,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787688</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787698</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2135,6 +2200,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787705</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2246,6 +2316,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787706</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2357,6 +2432,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787721</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2473,6 +2553,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787737</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2584,6 +2669,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787748</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2700,6 +2790,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787772</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2821,6 +2916,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787777</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2932,6 +3032,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118794857</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3053,6 +3158,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73371295</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3155,6 +3265,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787583</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3257,6 +3372,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787586</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3359,6 +3479,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787593</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3461,6 +3586,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787627</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3563,6 +3693,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787632</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3665,6 +3800,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787637</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3776,6 +3916,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787641</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3878,6 +4023,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787642</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3980,6 +4130,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787669</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4082,6 +4237,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787670</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4184,6 +4344,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787673</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4286,6 +4451,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787677</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4393,6 +4563,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787680</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4495,6 +4670,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787686</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4597,6 +4777,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787693</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4699,6 +4884,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787710</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4801,6 +4991,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787722</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4903,6 +5098,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787724</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5005,6 +5205,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787726</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5107,6 +5312,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787729</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5209,6 +5419,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787731</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5311,6 +5526,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787734</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5413,6 +5633,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787747</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5515,6 +5740,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787751</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5617,6 +5847,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787580</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5719,6 +5954,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787684</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5821,6 +6061,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787704</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5923,6 +6168,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787707</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6025,6 +6275,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787752</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6127,6 +6382,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787645</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6229,6 +6489,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787653</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6336,6 +6601,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787755</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6438,6 +6708,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787576</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6540,6 +6815,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787581</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6642,6 +6922,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787585</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6744,6 +7029,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787588</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6846,6 +7136,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787591</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6948,6 +7243,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787592</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7050,6 +7350,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787594</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7152,6 +7457,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787595</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7254,6 +7564,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787600</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7356,6 +7671,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787603</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7458,6 +7778,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787604</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7560,6 +7885,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787609</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7662,6 +7992,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787616</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7764,6 +8099,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787617</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7866,6 +8206,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787628</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7968,6 +8313,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787630</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8070,6 +8420,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787633</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8172,6 +8527,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787639</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8274,6 +8634,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787649</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8381,6 +8746,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787668</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8483,6 +8853,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787671</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8585,6 +8960,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787678</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8687,6 +9067,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787681</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8789,6 +9174,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787682</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8891,6 +9281,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787694</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8993,6 +9388,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787695</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9095,6 +9495,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787700</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9197,6 +9602,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787711</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9299,6 +9709,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787713</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9401,6 +9816,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787719</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9503,6 +9923,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787725</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9605,6 +10030,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787727</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9707,6 +10137,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787730</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9809,6 +10244,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787732</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9911,6 +10351,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787735</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10013,6 +10458,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787736</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10115,6 +10565,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787749</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10217,6 +10672,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787753</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10319,6 +10779,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787584</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10421,6 +10886,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787587</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10523,6 +10993,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787590</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10625,6 +11100,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787596</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10727,6 +11207,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787599</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10829,6 +11314,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787608</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10931,6 +11421,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787613</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11033,6 +11528,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787622</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11135,6 +11635,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787708</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11237,6 +11742,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787712</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11339,6 +11849,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787718</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11441,6 +11956,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787733</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11543,6 +12063,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787750</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11645,6 +12170,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787754</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11752,6 +12282,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787756</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11868,6 +12403,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787579</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11984,6 +12524,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787720</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12100,6 +12645,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787743</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12202,6 +12752,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787643</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12313,6 +12868,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787703</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12424,8 +12984,127 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118787709</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>